--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,32 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +140,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,34 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -810,20 +777,20 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -859,10 +826,10 @@
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v>22</v>
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.6</v>
@@ -874,7 +841,7 @@
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.3</v>
+        <v>142.3</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>2.1</v>
@@ -895,16 +862,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G5" s="9" t="n">
+      <c r="D5" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -917,13 +884,13 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.9</v>
+        <v>19.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -932,22 +899,22 @@
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -962,7 +929,7 @@
         <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -980,16 +947,16 @@
       <c r="C6" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" s="9" t="n">
+      <c r="D6" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -1002,7 +969,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>21.6</v>
@@ -1014,7 +981,7 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.7</v>
@@ -1026,7 +993,7 @@
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>27.3</v>
+        <v>22.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.6</v>
@@ -1040,14 +1007,14 @@
       <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
+      <c r="X6" s="12" t="n">
+        <v>92</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1065,74 +1032,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>11.4</v>
+      <c r="G7" s="10" t="n">
+        <v>11.5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2.1</v>
+        <v>34.5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>96.5</v>
+        <v>6.5</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>11.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>28</v>
+        <v>25.6</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.5</v>
+        <v>54.8</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>73.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1150,74 +1117,74 @@
       <c r="C8" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>11.5</v>
+      <c r="E8" s="11" t="n">
+        <v>-62.4</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>-79.3</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>54.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20.6</v>
+        <v>60.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.8</v>
+        <v>20.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>22.1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>21.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>25.7</v>
+        <v>28.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>812.1</v>
+        <v>870.6</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>33.3</v>
+        <v>344.6</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>27.9</v>
+        <v>24.4</v>
+      </c>
+      <c r="S8" s="12" t="n">
+        <v>57.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>54.8</v>
+        <v>308</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>28.1</v>
+        <v>96.09999999999999</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>35.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>28.2</v>
+        <v>39.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>74.2</v>
+        <v>389.1</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1236,76 +1203,76 @@
         <v>1783.6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>161.7</v>
+        <v>32.3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>107.4</v>
+        <v>21.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>54.3</v>
+        <v>26.9</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.8</v>
+        <v>26.4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>20.9</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>109.4</v>
+        <v>21.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.2</v>
+        <v>21.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.3</v>
+        <v>25.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>3.1</v>
+        <v>927.4</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 066
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>155.6</v>
+        <v>344.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>44.4</v>
+        <v>24.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308 10
-</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>61.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>135.7</v>
+        <v>2.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>272.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>389.1</v>
+        <v>22.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1327,68 +1294,70 @@
         <v>32.3</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>10.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>20.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>31.1</v>
+        <v>33.2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>18</v>
+        <v>563.5</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1404,76 +1373,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>420.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>33.13</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>426.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.8</v>
+        <v>23.3</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>933.2</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>56.3</v>
+        <v>58</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>29.5</v>
+        <v>20.8</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1491,74 +1460,74 @@
       <c r="C12" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>12.6</v>
+      <c r="D12" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.8</v>
+        <v>11.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>23.3</v>
+        <v>21</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>210.4</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.7</v>
+        <v>67.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.8</v>
+        <v>24.3</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>158</v>
+        <v>62.9</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.8</v>
+        <v>13</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>29.6</v>
+        <v>26.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>30.3</v>
+        <v>23.8</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>73.2</v>
+        <v>80.8</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>6.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1574,76 +1543,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>2362.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>97</v>
+        <v>998</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>29.1</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>72.3</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1659,76 +1628,80 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+1
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>60.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>21.1</v>
+        <v>13.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>20.9</v>
+        <v>19.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>9.6</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>27.3</v>
+        <v>6.2</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>60</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.8</v>
+        <v>41</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>8.1</v>
+        <v>12.3</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1746,74 +1719,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>12.1</v>
+      <c r="E15" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>54.5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>2.9</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>22.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>33.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>496</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>30</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>51.4</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>30</v>
+        <v>42.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>71</v>
+        <v>331</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>25</v>
+        <v>76.3</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>36.5</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>21.9</v>
+        <v>1.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>24.3</v>
+        <v>75.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>386.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.4</v>
+        <v>42.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1829,76 +1802,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5304.1</v>
+        <v>1530.8</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>154</v>
+        <v>54.5</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>99</v>
+        <v>199.2</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>54.5</v>
+        <v>5.4</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>19.7</v>
+        <v>32.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>16.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>28.9</v>
+        <v>206.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.9</v>
+        <v>20.4</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>490</v>
+        <v>98</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>152.4</v>
+        <v>3606.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>85.8</v>
+        <v>25.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.4</v>
+        <v>28.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
+        <v>15.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>136.5</v>
+        <v>22.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.4</v>
+        <v>24.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>386.1</v>
+        <v>725.6</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1914,76 +1887,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
+        <v>606.4</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>30.8</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>19.9</v>
+        <v>9.4</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>10.9</v>
+        <v>25.7</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>20.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>39.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>30.5</v>
+        <v>32.2</v>
       </c>
       <c r="R17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="X17" s="3" t="n">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1999,76 +1972,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>17.2</v>
+        <v>336.5</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>19.4</v>
+        <v>42.1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>20.1</v>
+        <v>18.4</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.1</v>
+        <v>0.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.6</v>
+        <v>88.5</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2084,76 +2057,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>18.8</v>
+        <v>299</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4.2</v>
+        <v>42.1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>21.7</v>
+        <v>2.9</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>60.5</v>
+        <v>1.6</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>25.7</v>
+        <v>10.6</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2169,76 +2142,76 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>35.5</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>6.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.8</v>
+        <v>18.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>99</v>
+        <v>1006.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>27.9</v>
+        <v>30.1</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.6</v>
+        <v>15.7</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>26.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>51.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2254,37 +2227,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>12.1</v>
+        <v>294.9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.9</v>
+        <v>3.5</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61 1
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>22.1</v>
@@ -2293,37 +2269,37 @@
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>26.9</v>
+        <v>22.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>63.1</v>
+        <v>66.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>463.1</v>
+        <v>24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2339,76 +2315,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R22" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>25.8</v>
-      </c>
       <c r="S22" s="3" t="n">
-        <v>29.9</v>
+        <v>39.7</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>24</v>
+        <v>320</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>29.3</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>22.6</v>
+        <v>78.3</v>
       </c>
       <c r="X22" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2424,76 +2400,79 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
+        <v>322</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>156</v>
+        <v>31.1</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>96.5</v>
+        <v>12.2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>125.5</v>
+        <v>25.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.8</v>
+        <v>11.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>17.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>972.8</v>
+        <v>19.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>122.7</v>
+        <v>22.7</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>98.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
+        <v>30.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1911.6</v>
+        <v>24.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3941.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>320</v>
+        <v>64</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1899.3</v>
+        <v>25.9</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>18.9</v>
+        <v>23.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>405.6</v>
+        <v>28.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>422</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2509,68 +2488,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
+        <v>0.1</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>31.2</v>
+        <v>30.1</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>11.9</v>
+        <v>24.9</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+15156
+</t>
+        </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>24.9</v>
+        <v>0.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X24" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2586,58 +2578,64 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>10.3</v>
+        <v>12.8</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>11.2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I25" s="3" t="n"/>
+        <v>18.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J25" s="3" t="n">
-        <v>41.3</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>31.6</v>
+        <v>14.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="12" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N25" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q25" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>15.2</v>
+        <v>1.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>21</v>
@@ -2646,10 +2644,10 @@
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95.2</v>
+        <v>952.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2667,35 +2665,35 @@
       <c r="C26" s="3" t="n">
         <v>345</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>11.2</v>
+      <c r="D26" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
@@ -2704,13 +2702,13 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>25.3</v>
@@ -2718,23 +2716,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>20.6</v>
+      <c r="U26" s="12" t="n">
+        <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>27.2</v>
+        <v>22.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.3</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2750,46 +2748,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>32.9</v>
+        <v>48.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>32.6</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>86.09999999999999</v>
+      <c r="F27" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.7</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>15.2</v>
+        <v>52.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
+        <v>994</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
@@ -2810,16 +2808,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>25.5</v>
+        <v>65.5</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>74.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2837,47 +2835,47 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>12.8</v>
+      <c r="F28" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.4</v>
+        <v>190.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>220.1</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2889,7 +2887,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2901,10 +2899,10 @@
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2922,29 +2920,29 @@
       <c r="C29" s="3" t="n">
         <v>140.2</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>24.8</v>
+      <c r="D29" s="11" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>2.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
@@ -2959,7 +2957,7 @@
         <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2971,7 +2969,7 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
@@ -2986,10 +2984,10 @@
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3008,52 +3006,52 @@
         <v>1363.5</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>156.4</v>
-      </c>
-      <c r="E30" s="22" t="n">
-        <v>99</v>
-      </c>
-      <c r="F30" s="22" t="n">
-        <v>28</v>
+        <v>4.4</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>996.1</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>25.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>56.9</v>
+        <v>1.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>0.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>17.9</v>
+        <v>172.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>23.7</v>
+        <v>5.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>102.2</v>
+        <v>20.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.7</v>
+        <v>172.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>489.5</v>
+        <v>429.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>3545.1</v>
+        <v>3.3</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3062,19 +3060,23 @@
         <v>68.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>26.7</v>
+        <v>15.3</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+4
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3093,53 +3095,58 @@
         <v>272.7</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F31" s="22" t="n">
-        <v>25.6</v>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>20.4</v>
+        <v>61.6</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>71.8</v>
+        <v>26.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>978.9</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>84.2</v>
+      <c r="Q31" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>22.1</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 89
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="n">
         <v>13.8</v>
@@ -3148,16 +3155,21 @@
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>23.1</v>
+        <v>0.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
+        <v>2.1</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+22
+171971191 7
+</t>
+        </is>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3175,32 +3187,32 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>8.6</v>
+      <c r="G32" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>21.5</v>
@@ -3211,7 +3223,9 @@
       <c r="O32" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P32" s="3" t="n"/>
+      <c r="P32" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
@@ -3219,16 +3233,16 @@
         <v>24.5</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>27.9</v>
+        <v>22.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>638.2</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>27.1</v>
+      <c r="V32" s="12" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>24.5</v>
@@ -3237,10 +3251,15 @@
         <v>25.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717177
+23
+83
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3258,32 +3277,32 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>29</v>
+      <c r="D33" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.8</v>
+        <v>2.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
@@ -3292,10 +3311,10 @@
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>98</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
@@ -3304,7 +3323,7 @@
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>83.40000000000001</v>
@@ -3322,10 +3341,10 @@
         <v>21.4</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>948.1</v>
+        <v>28.7</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3341,47 +3360,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E34" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+      <c r="F34" s="11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>20.1</v>
+        <v>19</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>61.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>980.8</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 20
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>25.6</v>
@@ -3390,13 +3414,13 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
+        <v>76.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>26.3</v>
+      <c r="V34" s="12" t="n">
+        <v>63.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>21</v>
@@ -3408,7 +3432,7 @@
         <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3426,38 +3450,44 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>10.7</v>
+      <c r="G35" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1.5</v>
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19</v>
+        <v>0.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3481,7 +3511,7 @@
         <v>9.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>66.3</v>
+        <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
@@ -3493,7 +3523,7 @@
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3511,29 +3541,39 @@
       <c r="C36" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D36" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.6</v>
+      <c r="F36" s="11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222725
+1142811042
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.3</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3542,13 +3582,13 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.8</v>
+        <v>20.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3565,20 +3605,20 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>21.4</v>
+      <c r="V36" s="12" t="n">
+        <v>41.4</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>24.2</v>
+        <v>4.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3594,16 +3634,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>826.4</v>
+        <v>22.6</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>142.9</v>
+        <v>7.7</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>121.5</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>42.9</v>
@@ -3615,34 +3655,39 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1203444.6</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>44.4</v>
+        <v>1034.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+22
+7
+</t>
+        </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>214.9</v>
+        <v>20.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
+        <v>1334.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>11287.9</v>
+        <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>27.3</v>
+        <v>86.3</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
@@ -3654,16 +3699,14 @@
         <v>124.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="n">
         <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3690,14 +3733,14 @@
       <c r="F38" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>8.6</v>
+      <c r="G38" s="10" t="n">
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>1.8</v>
@@ -3707,7 +3750,7 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.6</v>
+        <v>61.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3716,17 +3759,19 @@
         <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>29.3</v>
+        <v>73.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
@@ -3735,13 +3780,13 @@
         <v>84.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>8324.799999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3760,72 +3805,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F39" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>545.5</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>19.5</v>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 29
+15
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.7</v>
+        <v>10.1</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>28.8</v>
+        <v>89.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>15.2</v>
+        <v>666.1</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>42.7</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>28</v>
+        <v>61.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3841,76 +3892,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>29.2</v>
+        <v>19.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>98.8</v>
+        <v>990.6</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>29.3</v>
+        <v>36.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>70.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>24.4</v>
+        <v>0.1</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3926,76 +3975,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>288.6</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>10.5</v>
+        <v>242.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>29.2</v>
+        <v>21</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+111
+</t>
+        </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30.9</v>
+        <v>29.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>21.7</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>20.5</v>
+      </c>
+      <c r="U41" s="12" t="n">
+        <v>26</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>29.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>81.8</v>
+        <v>24.4</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4011,74 +4064,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>25.9</v>
+        <v>288.6</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="K42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>10618.2</v>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="3" t="n">
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>84.3</v>
-      </c>
       <c r="Z42" s="3" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4094,29 +4149,31 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>25.9</v>
+      <c r="E43" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="K43" s="3" t="n">
-        <v>39.5</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
@@ -4125,31 +4182,41 @@
       <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="R43" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77</v>
+        <v>726</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>95.09999999999999</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>392.3</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>32.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4165,55 +4232,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>934.6</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>311.6</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>546.5</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n">
-        <v>491.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q44" s="8" t="n">
-        <v>2461.2</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>6.4</v>
+      </c>
+      <c r="Q44" s="12" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>726</v>
+      </c>
       <c r="U44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>32.3</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="X44" s="12" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>3242.3</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4228,58 +4319,60 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>290.7</v>
-      </c>
-      <c r="D45" s="22" t="n">
-        <v>305.1</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>155</v>
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>779.7</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>153</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.1</v>
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>934.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="n">
+        <v>45.9</v>
+      </c>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="n">
+        <v>113.8</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>24.1</v>
+        <v>4.4</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>494.2</v>
+      </c>
+      <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>29.3</v>
+        <v>146.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>64.5</v>
+        <v>24.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>27.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>68.3</v>
+        <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>13.2</v>
+        <v>66.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>26.8</v>
+        <v>71.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>23.8</v>
@@ -4288,10 +4381,10 @@
         <v>27.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>78.5</v>
+        <v>3242.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>7.7</v>
+        <v>38.3</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4306,56 +4399,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="C46" s="3" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G46" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>16.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>20.8</v>
+      <c r="K46" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>68.40000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="U46" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,25 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -777,74 +792,74 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="12" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>6.6</v>
+      <c r="H4" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.6</v>
+        <v>21.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>28.1</v>
+      <c r="S4" s="8" t="n">
+        <v>1281.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>142.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -862,16 +877,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -884,52 +899,52 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>25.4</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -945,58 +960,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>10.3</v>
+        <v>12368</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>41</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>988.5</v>
+        <v>197</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>22.3</v>
+        <v>41.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>59.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>18.6</v>
@@ -1004,17 +1017,17 @@
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="12" t="n">
-        <v>92</v>
+      <c r="X6" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1032,74 +1045,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="D7" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>20.6</v>
+      <c r="G7" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>944.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6.5</v>
+        <v>1980.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>72.90000000000001</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>23</v>
+        <v>159.5</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,76 +1128,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>19368</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>-62.4</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>-79.3</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="R8" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>870.6</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S8" s="12" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="V8" s="12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>39.5</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>389.1</v>
+        <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>41.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1200,79 +1213,58 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.6</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>26.4</v>
-      </c>
+        <v>17183.6</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="n">
-        <v>2.4</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>4.2</v>
+        <v>120.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>25.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>927.4</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>4.5</v>
+        <v>1371.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>61.6</v>
+        <v>908</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>190.1</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="n">
-        <v>272.9</v>
+        <v>1032.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>22.8</v>
+        <v>1389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>8.4</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1288,76 +1280,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="9" t="n">
+        <v>2356.7</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>18.7</v>
+      <c r="E10" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>563.5</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>29</v>
+      <c r="X10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>9.4</v>
+        <v>177.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>2.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1373,76 +1363,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>426.3</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>18.6</v>
+        <v>453.1</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" s="3" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>28.7</v>
+      <c r="S11" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.6</v>
+        <v>156.3</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>655.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>3.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1458,76 +1448,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>141824</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>26.4</v>
+      <c r="V12" s="8" t="n">
+        <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X12" s="12" t="n">
-        <v>72.8</v>
+        <v>25.6</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80.8</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1543,76 +1533,74 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2362.1</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>17.8</v>
+        <v>1230.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>24.6</v>
+      <c r="K13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>998</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>28.2</v>
+        <v>197</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="8" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>28.6</v>
-      </c>
       <c r="Y13" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>5</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1628,80 +1616,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.4</v>
+        <v>1821.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.5</v>
+        <v>18.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>9.6</v>
+        <v>198</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>41</v>
+        <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>12.3</v>
+        <v>18.1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>24.3</v>
+        <v>24</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1719,74 +1703,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>54.5</v>
+      <c r="D15" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.5</v>
+        <v>94.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>33.7</v>
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>51.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>42.7</v>
+        <v>25.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>75.8</v>
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>386.1</v>
+        <v>16.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>42.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1801,77 +1785,59 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>1530.8</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>10.7</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="12" t="n">
+        <v>154</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>15.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.4</v>
+        <v>192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>32.9</v>
+        <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>186.4</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>98</v>
+        <v>1490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3606.5</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>152.4</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>66.8</v>
+        <v>1331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>176.3</v>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>725.6</v>
+        <v>1386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>8.5</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1887,76 +1853,72 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>606.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>13</v>
+      <c r="E17" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.5</v>
+        <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>39.4</v>
+        <v>20.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>32.2</v>
+        <v>90.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>58</v>
+        <v>166.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>15.3</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>6.1</v>
+        <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.6</v>
+        <v>1717.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.6</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1972,76 +1934,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>336.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>18.8</v>
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>67.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>20.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>42.1</v>
+        <v>14</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>28.2</v>
+      <c r="S18" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>25.2</v>
+        <v>158</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>29.2</v>
+        <v>25.1</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>229.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>88.5</v>
+        <v>177.6</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2057,76 +2019,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>10</v>
+        <v>1326.2</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>26.3</v>
+      <c r="V19" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83</v>
+        <v>188.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2142,76 +2104,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>24.5</v>
+        <v>1299</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>24.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>6.4</v>
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.8</v>
+        <v>31.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>1006.8</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>24.4</v>
+      <c r="Q20" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>238.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>63.4</v>
+        <v>171.6</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="Y20" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>183</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>35.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2227,79 +2187,74 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>12.4</v>
-      </c>
+        <v>1357.5</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61 1
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>19.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>25.8</v>
+        <v>1001</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>66.8</v>
+        <v>163.1</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>88.8</v>
+        <v>184.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2315,76 +2270,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>88.2</v>
+        <v>1294.9</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>531.2</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>10.1</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>97.8</v>
+        <v>19.1</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>7.3</v>
+        <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q22" s="12" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R22" s="12" t="n">
-        <v>24.6</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>39.7</v>
+        <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>320</v>
+        <v>166.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>10.6</v>
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>216.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>442</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>26.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2399,80 +2352,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="16" t="inlineStr"/>
+      <c r="E23" s="16" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>11.9</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17.6</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>198.4</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>1252.9</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>64</v>
+        <v>1320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>28.1</v>
-      </c>
+        <v>179.6</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.2</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2488,81 +2412,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F24" s="9" t="n">
+        <v>322</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>988.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.1</v>
+      <c r="S24" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>164</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.4</v>
+        <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>0.1</v>
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.1</v>
+        <v>184.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.1</v>
+        <v>55.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2578,76 +2493,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="N25" s="12" t="n">
+      <c r="M25" s="3" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>6.9</v>
+        <v>22.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>23.6</v>
+        <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>952.6</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2663,43 +2576,41 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>68.61</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.1</v>
-      </c>
+        <v>2345</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
@@ -2707,7 +2618,7 @@
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2716,23 +2627,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
+      <c r="U26" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>26.8</v>
+        <v>62.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>4.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2748,31 +2659,29 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>32.6</v>
+        <v>2418.2</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>26.8</v>
+        <v>5.4</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>52.4</v>
+        <v>5.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2780,26 +2689,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>994</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2807,17 +2716,17 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
+      <c r="W27" s="8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.2</v>
+        <v>174.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>4.3</v>
+        <v>110.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2835,74 +2744,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="D28" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E28" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>190.8</v>
+      <c r="F28" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
+        <v>12.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="12" t="n">
-        <v>29.9</v>
+      <c r="M28" s="3" t="n">
+        <v>49.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>23.1</v>
+        <v>33.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>29.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>169.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
+      <c r="X28" s="8" t="n">
+        <v>260.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.8</v>
+        <v>14.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2918,76 +2827,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>5.2</v>
+        <v>120.2</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.2</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>23.7</v>
+        <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3.7</v>
+        <v>173.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W29" s="3" t="n">
+      <c r="V29" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>21.6</v>
+        <v>181.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3002,81 +2911,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>1363.5</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>996.1</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.4</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr"/>
+      <c r="E30" s="16" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="17" t="n">
+        <v>50.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.4</v>
+        <v>192.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>172.1</v>
+        <v>16.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>172.8</v>
-      </c>
+        <v>123.7</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>429.5</v>
+        <v>1489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>344.5</v>
+        <v>1344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
-      </c>
+        <v>168.8</v>
+      </c>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>1411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3094,82 +2973,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F31" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>19.4</v>
+      <c r="D31" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.3</v>
+        <v>20.1</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>978.9</v>
+        <v>197.9</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q31" s="12" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 89
-</t>
-        </is>
+        <v>10.2</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>168.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>13.8</v>
+        <v>63.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
-        </is>
+        <v>255.1</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>181.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3185,81 +3054,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>1263.5</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>19</v>
+      <c r="G32" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="M32" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99</v>
+        <v>990.1</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>22.9</v>
+      <c r="S32" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>69.8</v>
+        <v>169.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="12" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="W32" s="3" t="n">
+      <c r="V32" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>25.8</v>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1717177
-23
-83
-</t>
-        </is>
+        <v>181.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3275,76 +3137,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.8</v>
+        <v>144.1</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.1</v>
+        <v>20.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>20.4</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>1.5</v>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>21.4</v>
+      <c r="X33" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.7</v>
+        <v>191.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3360,79 +3218,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>13.6</v>
+        <v>1117.8</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>167.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>61.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>76.2</v>
+        <v>70.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="W34" s="3" t="n">
+      <c r="V34" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>29.3</v>
+        <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.5</v>
+        <v>162.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3448,64 +3301,56 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>1284.4</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+      <c r="G35" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>25.8</v>
+        <v>243.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3517,13 +3362,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>24.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1.3</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3539,41 +3384,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>43.9</v>
+        <v>1117.2</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222725
-1142811042
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+        <v>72.5</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3581,14 +3416,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>20.9</v>
+      <c r="N36" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3600,25 +3435,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="12" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="W36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3634,79 +3469,58 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>42.9</v>
+        <v>826.4</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>143</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>14.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>17.3</v>
+        <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1034.4</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>103.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>86.3</v>
-      </c>
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
+        <v>140.4</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>1416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.7</v>
+        <v>128</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3722,71 +3536,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>18.6</v>
+      <c r="G38" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K38" s="3" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>61.3</v>
+        <v>20</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>73.5</v>
+      <c r="S38" s="8" t="n">
+        <v>927.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8324.799999999999</v>
+        <v>1839.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3805,78 +3617,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F39" s="10" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F39" s="17" t="n">
         <v>25</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>18</v>
+      <c r="H39" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 29
-15
-</t>
-        </is>
+        <v>93.5</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.6</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>130.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>666.1</v>
-      </c>
-      <c r="U39" s="12" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>61.2</v>
+        <v>166.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>2.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.1</v>
+        <v>106.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3892,71 +3702,73 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>44.8</v>
+        <v>278.1</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>30.8</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F40" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N40" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>990.6</v>
+        <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>165.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.1</v>
+        <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -3977,78 +3789,74 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F41" s="10" t="n">
+      <c r="D41" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
+      <c r="I41" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
+        <v>16.9</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98.8</v>
+        <v>193.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22.1</v>
+        <v>720.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>645.1</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>24.4</v>
+        <v>1841.1</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4066,74 +3874,74 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F42" s="10" t="n">
+      <c r="D42" s="12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>18.6</v>
+      <c r="H42" s="8" t="n">
+        <v>188.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>1.5</v>
+        <v>16.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>52.8</v>
+        <v>21.2</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10618.2</v>
+        <v>1600</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>0.4</v>
+        <v>162</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>207.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>29.3</v>
+      <c r="X42" s="8" t="n">
+        <v>239.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0.2</v>
+        <v>181.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4149,74 +3957,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>2311.6</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="E43" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n">
+      <c r="M43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N43" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S43" s="3" t="n">
+      <c r="R43" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>726</v>
+        <v>17</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>2.9</v>
+        <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>84.3</v>
+        <v>184.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4231,80 +4039,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>546.5</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q44" s="12" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R44" s="12" t="n">
-        <v>373.3</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="X44" s="12" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>3242.3</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4319,72 +4077,54 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>779.7</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>153</v>
-      </c>
+        <v>1722.7</v>
+      </c>
+      <c r="D45" s="16" t="inlineStr"/>
+      <c r="E45" s="16" t="inlineStr"/>
+      <c r="F45" s="16" t="inlineStr"/>
       <c r="G45" s="3" t="n">
-        <v>50.6</v>
+        <v>6.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>293.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>164.9</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>494.2</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>191.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
+        <v>146.2</v>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>27.6</v>
-      </c>
+        <v>1668</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>3242.3</v>
+        <v>992.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.3</v>
+        <v>198.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4402,74 +4142,72 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>20.5</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G46" s="10" t="n">
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="8" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>18.7</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>10.5</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.4</v>
+        <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S46" s="12" t="n">
-        <v>77.2</v>
+        <v>645.1</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>32.4</v>
+        <v>168.3</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>292.2</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>26.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
@@ -61,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,34 +149,55 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -792,75 +813,73 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
+        <v>22.1</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>27.4</v>
+      <c r="N4" s="8" t="n">
+        <v>76.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="8" t="n">
-        <v>1.7</v>
+      <c r="P4" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>1281.1</v>
+      <c r="S4" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>174.3</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>110</v>
-      </c>
+        <v>1754.3</v>
+      </c>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -877,61 +896,61 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.5</v>
+        <v>25.4</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V5" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -941,7 +960,7 @@
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>2.1</v>
@@ -960,74 +979,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12368</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E6" s="12" t="n">
+        <v>268.1</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>41</v>
+      <c r="F6" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>197</v>
+        <v>92</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>41.3</v>
+        <v>27.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1045,29 +1066,29 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="D7" s="11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>944.4</v>
+      <c r="H7" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20.3</v>
+        <v>2.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>11.3</v>
+        <v>21.8</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1076,33 +1097,33 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46.1</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>311.9</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>159.5</v>
+        <v>59.5</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>19.1</v>
+        <v>29.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
@@ -1128,19 +1149,19 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19368</v>
-      </c>
-      <c r="D8" s="12" t="n">
+        <v>9681.1</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>33.2</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>11.5</v>
+      <c r="E8" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
@@ -1149,39 +1170,39 @@
         <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>41.7</v>
+      <c r="M8" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1190,7 +1211,7 @@
       <c r="W8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="8" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1213,55 +1234,73 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>17183.6</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+        <v>1185</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>12100.8</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>120.9</v>
+        <v>20.9</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>128.2</v>
+      </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>124.4</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>1371.5</v>
+        <v>153790.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>908</v>
+        <v>308</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>1420</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>1032.5</v>
+        <v>1139.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1389.1</v>
+        <v>589.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1280,30 +1319,30 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2356.7</v>
-      </c>
-      <c r="D10" s="12" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="H10" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="8" t="n">
+        <v>17.5</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>21.9</v>
       </c>
@@ -1314,37 +1353,37 @@
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>197.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>161.6</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>177.8</v>
+        <v>1417.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1363,34 +1402,34 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>453.1</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E11" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>13.8</v>
+      <c r="G11" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>10.4</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1399,10 +1438,10 @@
         <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>33.2</v>
@@ -1410,26 +1449,26 @@
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>156.3</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>655.1</v>
+      <c r="W11" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>12.2</v>
@@ -1448,43 +1487,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>141824</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>1218.2</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>220.3</v>
+      <c r="N12" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.7</v>
@@ -1499,12 +1538,12 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1958</v>
-      </c>
-      <c r="U12" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1514,10 +1553,10 @@
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>713.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>111.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1533,61 +1572,63 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1230.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="12" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K13" s="8" t="n">
+      <c r="J13" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="R13" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="S13" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1597,10 +1638,10 @@
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>800.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1616,52 +1657,52 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1821.4</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>821.4</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>87.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>41.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>24.8</v>
+      <c r="R14" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>28.2</v>
@@ -1670,7 +1711,7 @@
         <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>26</v>
@@ -1678,14 +1719,14 @@
       <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>185.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1703,74 +1744,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>12.1</v>
+      <c r="D15" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="N15" s="8" t="n">
+      <c r="M15" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="8" t="n">
+      <c r="U15" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16.6</v>
+        <v>716.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1785,59 +1826,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>154</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>15.4</v>
+      <c r="C16" s="3" t="n">
+        <v>15308.1</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>52.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>192.1</v>
+        <v>19.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>162.4</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1129</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>1490</v>
+        <v>490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>142.7</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>1331</v>
+        <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>140</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1386.1</v>
+        <v>13861.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>42.3</v>
+        <v>14.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1855,70 +1914,74 @@
       <c r="C17" s="3" t="n">
         <v>306.2</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="D17" s="11" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="F17" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>23.8</v>
+      <c r="N17" s="8" t="n">
+        <v>888.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>90.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>166.2</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="V17" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="n">
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1717.2</v>
+        <v>141.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,76 +1997,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="12" t="n">
+        <v>3341.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="11" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>67.2</v>
+        <v>171.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>20.4</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>19.7</v>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>69.7</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V18" s="8" t="n">
+      <c r="U18" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>229.8</v>
+        <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>177.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2019,43 +2082,43 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1326.2</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" s="12" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>24.3</v>
+      <c r="N19" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.4</v>
@@ -2064,15 +2127,15 @@
         <v>31.7</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S19" s="8" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="S19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="U19" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U19" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="V19" s="8" t="n">
@@ -2081,11 +2144,11 @@
       <c r="W19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.8</v>
@@ -2104,56 +2167,58 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="F20" s="17" t="n">
+        <v>2899</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="11" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>31.5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>22.8</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>238.4</v>
+      <c r="R20" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>171.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.6</v>
@@ -2164,11 +2229,11 @@
       <c r="W20" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>5.4</v>
@@ -2187,56 +2252,58 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1357.5</v>
-      </c>
-      <c r="D21" s="12" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="G21" s="15" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>16.4</v>
+      </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
+        <v>12.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>12.8</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>163.1</v>
+        <v>63.1</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>15.7</v>
@@ -2244,17 +2311,17 @@
       <c r="V21" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>184.1</v>
+        <v>18484.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2270,32 +2337,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1294.9</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>531.2</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>992.9</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17.4</v>
+        <v>11.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="K22" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2304,12 +2373,12 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>31</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2319,19 +2388,19 @@
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>216.5</v>
+      <c r="X22" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>88.8</v>
@@ -2352,15 +2421,23 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1610.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>125.8</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2368,35 +2445,53 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>16.5</v>
+      </c>
       <c r="L23" s="3" t="n">
-        <v>198.4</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1613.3</v>
+      </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>152.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>115394.7</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>1320</v>
+        <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>796.1</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>140.6</v>
+      </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>126.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2412,54 +2507,56 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D24" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F24" s="12" t="n">
+      <c r="E24" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="11" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>1.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="8" t="n">
-        <v>29.7</v>
+      <c r="L24" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>22.7</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>988.1</v>
+        <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="R24" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2467,17 +2564,17 @@
       <c r="V24" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>55.3</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2493,44 +2590,46 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>4.4</v>
+        <v>171.8</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>17.6</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
@@ -2538,29 +2637,29 @@
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>95.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2576,29 +2675,31 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>845</v>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>886.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2610,19 +2711,19 @@
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>55.2</v>
@@ -2630,17 +2731,17 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>62.1</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>174.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2659,29 +2760,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D27" s="17" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H27" s="3" t="n">
+        <v>1418.2</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="n">
+        <v>13.1</v>
+      </c>
       <c r="J27" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2689,26 +2792,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2717,16 +2820,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>174.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>110.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2744,74 +2847,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>12.6</v>
+        <v>80</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>49.9</v>
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>33.4</v>
+        <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>29.7</v>
+        <v>979.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>224.4</v>
-      </c>
-      <c r="W28" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>260.3</v>
+        <v>659.5</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>0.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2827,48 +2930,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="12" t="n">
+        <v>122112.1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="11" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
+      <c r="M29" s="3" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="N29" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
@@ -2878,25 +2979,25 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.8</v>
+        <v>181.9</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2911,48 +3012,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="16" t="inlineStr"/>
-      <c r="E30" s="16" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr"/>
-      <c r="G30" s="17" t="n">
-        <v>50.7</v>
+      <c r="C30" s="3" t="n">
+        <v>625.1</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>57</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>192.2</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.7</v>
+        <v>114.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>123.7</v>
       </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>122.8</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>1489.5</v>
+        <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>1344.5</v>
+        <v>344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>68.8</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>13.3</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>1411.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -2973,72 +3100,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="D31" s="11" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>11.9</v>
+      <c r="F31" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>197.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>255.1</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>23.1</v>
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>206.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>181.3</v>
+        <v>182.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>1682.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3054,41 +3181,43 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1263.5</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D32" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>990.1</v>
+        <v>99</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3096,32 +3225,32 @@
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>169.8</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>29.1</v>
+      <c r="X32" s="3" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3137,29 +3266,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>144.1</v>
-      </c>
-      <c r="D33" s="12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D33" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>129</v>
+      <c r="G33" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
+      <c r="J33" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3167,42 +3298,44 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3218,22 +3351,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1117.8</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F34" s="12" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F34" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>167.8</v>
+        <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
@@ -3252,40 +3385,40 @@
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>162.5</v>
+        <v>62.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>182.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3301,41 +3434,43 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1284.4</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>10.7</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="n">
-        <v>243.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>10</v>
@@ -3343,14 +3478,14 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>275.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3361,14 +3496,14 @@
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>29.3</v>
+      <c r="X35" s="8" t="n">
+        <v>2959.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>164.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3386,20 +3521,20 @@
       <c r="C36" s="3" t="n">
         <v>1117.2</v>
       </c>
-      <c r="D36" s="12" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F36" s="12" t="n">
+      <c r="D36" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>72.5</v>
+      <c r="G36" s="11" t="n">
+        <v>7.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3408,7 +3543,7 @@
         <v>11</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>16.3</v>
+        <v>11.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3416,14 +3551,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3435,25 +3570,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>15.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3471,53 +3606,71 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="F37" s="12" t="n">
+      <c r="D37" s="11" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>14.3</v>
+      <c r="G37" s="11" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="K37" s="3" t="n">
         <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="P37" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>233.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>136.3</v>
+      </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+        <v>40.4</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>129.8</v>
+      </c>
       <c r="Y37" s="3" t="n">
-        <v>1416</v>
+        <v>12466</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128</v>
@@ -3536,69 +3689,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>68.59999999999999</v>
+      <c r="H38" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>927.3</v>
+      <c r="S38" s="3" t="n">
+        <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
+        <v>828.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1839.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3617,31 +3774,31 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F39" s="17" t="n">
+        <v>332</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="11" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>93.5</v>
+        <v>9.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.5</v>
@@ -3653,13 +3810,13 @@
         <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>130.7</v>
+        <v>0.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
@@ -3668,25 +3825,25 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>166.5</v>
+        <v>6685.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>27.2</v>
+        <v>17.8</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>106.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3702,76 +3859,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.1</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="D40" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+      <c r="H40" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>25.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V40" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>1811.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3787,77 +3944,75 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D41" s="12" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>18.8</v>
+      <c r="G41" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>18.5</v>
+      <c r="I41" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>193.8</v>
+        <v>93.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
-      </c>
-      <c r="U41" s="8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="8" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>645.1</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>1841.1</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>16.7</v>
-      </c>
+        <v>181.1</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3874,68 +4029,68 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="D42" s="11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>0.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>91.2</v>
+      <c r="M42" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q42" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>207.1</v>
+      <c r="V42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>239.3</v>
+        <v>8953.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>181.8</v>
@@ -3957,24 +4112,26 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2311.6</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F43" s="12" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F43" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>41.6</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
       </c>
@@ -3984,47 +4141,47 @@
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N43" s="8" t="n">
+      <c r="M43" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>35.4</v>
+        <v>95.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>184.3</v>
+        <v>1849.5</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4039,10 +4196,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4077,54 +4236,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1722.7</v>
-      </c>
-      <c r="D45" s="16" t="inlineStr"/>
-      <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr"/>
-      <c r="G45" s="3" t="n">
-        <v>6.1</v>
+        <v>1423.4</v>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>922.7</v>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F45" s="25" t="n">
+        <v>10101.1</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>1210.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>293.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>164.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>100900160.4</v>
+      </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>16128.5</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>191.8</v>
+        <v>4916</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1246.3</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1668</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>1412.4</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>122.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>992.3</v>
+        <v>3983.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>198.5</v>
+        <v>10820.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4142,72 +4321,74 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F46" s="12" t="n">
+      <c r="E46" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F46" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>18.7</v>
+        <v>11.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>20.6</v>
+      <c r="M46" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>198.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>29.3</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>645.1</v>
+        <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>27.7</v>
+        <v>71.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>22.6</v>
+        <v>73.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>18.5</v>
+        <v>128.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>7.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,19 +149,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,31 +176,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -813,16 +810,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="D4" s="9" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -832,7 +829,7 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>22.1</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -843,14 +840,14 @@
       <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>76.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.7</v>
+        <v>6.1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
@@ -858,7 +855,7 @@
       <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -873,11 +870,11 @@
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>29.1</v>
+      <c r="X4" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1754.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -896,26 +893,26 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F5" s="11" t="n">
+      <c r="D5" s="9" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>31.1</v>
+        <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
@@ -923,8 +920,8 @@
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>21.4</v>
+      <c r="M5" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -945,7 +942,7 @@
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>8.4</v>
@@ -956,7 +953,7 @@
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
@@ -979,19 +976,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>268.1</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E6" s="11" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>10.3</v>
+      <c r="F6" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -1000,7 +997,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1015,13 +1012,13 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>972</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
-        <v>12.4</v>
+      <c r="Q6" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>24.9</v>
@@ -1033,7 +1030,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
@@ -1045,10 +1042,10 @@
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>45.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1064,31 +1061,31 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E7" s="11" t="n">
+        <v>8218.200000000001</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G7" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1117,8 +1114,8 @@
       <c r="T7" s="3" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="8" t="n">
-        <v>29.1</v>
+      <c r="U7" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
@@ -1149,31 +1146,31 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9681.1</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>12.5</v>
+        <v>368</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>22.1</v>
@@ -1185,7 +1182,7 @@
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>10.9</v>
@@ -1200,7 +1197,7 @@
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>94.8</v>
+        <v>4.8</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>23</v>
@@ -1218,7 +1215,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1234,22 +1231,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>165.4</v>
-      </c>
-      <c r="E9" s="11" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>136.5</v>
+      <c r="F9" s="9" t="n">
+        <v>134.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12100.8</v>
+        <v>100.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>12</v>
@@ -1264,10 +1261,10 @@
         <v>109.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>128.2</v>
+        <v>12.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
@@ -1276,13 +1273,13 @@
         <v>13.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>156.6</v>
+        <v>8556.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>153790.5</v>
+        <v>127.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1291,16 +1288,16 @@
         <v>90.09999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>122</v>
+        <v>32.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1420</v>
+        <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1139.5</v>
+        <v>13.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>589.1</v>
+        <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1319,32 +1316,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>256.7</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>17.5</v>
+      <c r="K10" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>21.6</v>
@@ -1368,7 +1367,7 @@
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>161.6</v>
+        <v>61.6</v>
       </c>
       <c r="U10" s="8" t="n">
         <v>18</v>
@@ -1376,14 +1375,14 @@
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1417.8</v>
+        <v>877.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1404,32 +1403,32 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>13.4</v>
+      <c r="G11" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>18.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1453,7 +1452,7 @@
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>156.3</v>
+        <v>256.3</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>22.1</v>
@@ -1471,7 +1470,7 @@
         <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>112.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1489,26 +1488,26 @@
       <c r="C12" s="3" t="n">
         <v>1218.2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="9" t="n">
         <v>12.6</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>4.8</v>
@@ -1520,7 +1519,7 @@
         <v>20.1</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>97</v>
@@ -1538,7 +1537,7 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>20.8</v>
@@ -1549,14 +1548,14 @@
       <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>13.2</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>111.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1572,25 +1571,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="11" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
@@ -1611,7 +1610,7 @@
         <v>97</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>18.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>29.1</v>
@@ -1634,11 +1633,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>800.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6.6</v>
@@ -1657,18 +1656,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>821.4</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G14" s="11" t="n">
+        <v>1221.4</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
@@ -1681,7 +1680,7 @@
         <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>21.1</v>
@@ -1723,10 +1722,10 @@
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1744,17 +1743,17 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>82.09999999999999</v>
+      <c r="D15" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
@@ -1762,11 +1761,11 @@
       <c r="I15" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J15" s="8" t="n">
-        <v>8</v>
+      <c r="J15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
@@ -1783,7 +1782,7 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1795,10 +1794,10 @@
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
+      <c r="U15" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1808,7 +1807,7 @@
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>716.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>7.4</v>
@@ -1829,38 +1828,38 @@
       <c r="C16" s="3" t="n">
         <v>15308.1</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>127.4</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>52.5</v>
+      <c r="D16" s="9" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>162.4</v>
+        <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>102.2</v>
+        <v>2.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1129</v>
+        <v>111.9</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>490</v>
@@ -1872,31 +1871,31 @@
         <v>152.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>125.7</v>
+        <v>25.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.7</v>
+        <v>14.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>412.6</v>
+        <v>12.6</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>251.2</v>
+        <v>212</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>13861.1</v>
+        <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1914,14 +1913,14 @@
       <c r="C17" s="3" t="n">
         <v>306.2</v>
       </c>
-      <c r="D17" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="D17" s="9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>25.6</v>
+      <c r="F17" s="9" t="n">
+        <v>25.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.9</v>
@@ -1936,7 +1935,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
@@ -1944,16 +1943,16 @@
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>888.6</v>
+      <c r="N17" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
@@ -1963,9 +1962,9 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>1966.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
@@ -1974,11 +1973,11 @@
       <c r="W17" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>141.2</v>
+        <v>772.2</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>18.5</v>
@@ -1999,23 +1998,23 @@
       <c r="C18" s="3" t="n">
         <v>3341.1</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="D18" s="9" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>171.4</v>
+      <c r="H18" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
@@ -2024,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>29.4</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
@@ -2048,7 +2047,7 @@
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20.1</v>
@@ -2059,14 +2058,14 @@
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2084,19 +2083,19 @@
       <c r="C19" s="3" t="n">
         <v>326.2</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2115,7 +2114,7 @@
         <v>20.7</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
@@ -2123,11 +2122,11 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="8" t="n">
-        <v>55.3</v>
+      <c r="R19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>28.2</v>
@@ -2135,13 +2134,13 @@
       <c r="T19" s="3" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2167,22 +2166,22 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2899</v>
-      </c>
-      <c r="D20" s="11" t="n">
+        <v>299</v>
+      </c>
+      <c r="D20" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2223,10 +2222,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2254,26 +2253,26 @@
       <c r="C21" s="3" t="n">
         <v>357.5</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="E21" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="H21" s="8" t="n">
+      <c r="G21" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.8</v>
+        <v>3.8</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2288,7 +2287,7 @@
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2314,14 +2313,14 @@
       <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18484.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2337,34 +2336,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>992.9</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="11" t="n">
+        <v>1492.9</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>19.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2373,13 +2372,13 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>10800</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>25.8</v>
@@ -2391,7 +2390,7 @@
         <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24</v>
@@ -2424,20 +2423,20 @@
       <c r="C23" s="3" t="n">
         <v>1610.1</v>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D23" s="9" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F23" s="9" t="n">
         <v>125.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2446,7 +2445,7 @@
         <v>18.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>98.40000000000001</v>
@@ -2455,7 +2454,7 @@
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1613.3</v>
+        <v>12.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2467,31 +2466,31 @@
         <v>152.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1240.6</v>
+        <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>115394.7</v>
+        <v>1139.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>796.1</v>
+        <v>795.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.3</v>
+        <v>29.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>12.8</v>
+        <v>118.2</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>140.6</v>
+        <v>141.5</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2507,34 +2506,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2544,7 +2543,7 @@
         <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>30.6</v>
@@ -2590,25 +2589,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>171.8</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
@@ -2616,11 +2615,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>20</v>
+      <c r="L25" s="8" t="n">
+        <v>110.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>19.8</v>
+        <v>494.4</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2649,7 +2648,7 @@
       <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2675,31 +2674,31 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>845</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D26" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>886.8</v>
+        <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2708,16 +2707,14 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.1</v>
@@ -2760,25 +2757,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1418.2</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>38.7</v>
+      <c r="G27" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
@@ -2792,7 +2789,7 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2819,11 +2816,11 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="8" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>30.2</v>
+      <c r="W27" s="3" t="n">
+        <v>655.1</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2847,20 +2844,20 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E28" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G28" s="11" t="n">
+      <c r="F28" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>1.9</v>
@@ -2869,7 +2866,7 @@
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
@@ -2886,8 +2883,8 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="8" t="n">
-        <v>979.8</v>
+      <c r="Q28" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2899,7 +2896,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.7</v>
+        <v>12.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2907,11 +2904,11 @@
       <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>659.5</v>
+      <c r="X28" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.2</v>
@@ -2930,18 +2927,18 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>122112.1</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="9" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2951,14 +2948,14 @@
         <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n">
-        <v>21.9</v>
+      <c r="L29" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>241.9</v>
+        <v>21.5</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>25.4</v>
@@ -2972,7 +2969,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2982,7 +2979,7 @@
         <v>73.7</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>51.5</v>
+        <v>7.3</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>25</v>
@@ -2990,14 +2987,14 @@
       <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.9</v>
+        <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3012,56 +3009,54 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>625.1</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>130.1</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>57</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="9" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="G30" s="16" t="n">
+        <v>56.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>922.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>114.8</v>
+        <v>11.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>123.7</v>
+        <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>180.2</v>
+        <v>2.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>110.2</v>
+        <v>10.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>122.8</v>
+        <v>111.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>14.5</v>
+        <v>75.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>312.1</v>
+        <v>122</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>183.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3100,19 +3095,17 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="11" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+      <c r="D31" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
+      <c r="F31" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3149,23 +3142,23 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>182.3</v>
+        <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1682.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3183,26 +3176,26 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3244,13 +3237,13 @@
         <v>24.5</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3266,18 +3259,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="D33" s="11" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="9" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3287,10 +3280,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3317,7 +3310,7 @@
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
@@ -3335,7 +3328,7 @@
         <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3353,16 +3346,16 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
@@ -3371,7 +3364,9 @@
       <c r="I34" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
@@ -3388,7 +3383,7 @@
         <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>30.1</v>
@@ -3400,25 +3395,25 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>20.6</v>
+        <v>70.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>182.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3436,16 +3431,16 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
       <c r="H35" s="8" t="n">
@@ -3460,14 +3455,14 @@
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>18.9</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3485,7 +3480,7 @@
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3497,13 +3492,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>2959.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>164.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3519,19 +3514,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>7.5</v>
+      <c r="G36" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>19</v>
@@ -3540,7 +3535,7 @@
         <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.3</v>
@@ -3558,7 +3553,7 @@
         <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3572,14 +3567,12 @@
       <c r="T36" s="3" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>20.8</v>
+        <v>61.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
@@ -3588,7 +3581,7 @@
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3606,16 +3599,16 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="9" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="9" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="11" t="n">
+      <c r="G37" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3625,55 +3618,55 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.9</v>
+        <v>1807.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>28.8</v>
+        <v>22.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>92</v>
+        <v>20.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.8</v>
+        <v>32.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>233.1</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>127.2</v>
+        <v>117.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>136.3</v>
+        <v>13.6</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>393.6</v>
+        <v>3923.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>124.1</v>
+        <v>24.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>11.2</v>
+        <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>129.8</v>
+        <v>12.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>12466</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3689,18 +3682,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3709,17 +3702,17 @@
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>11.8</v>
+      <c r="J38" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3730,32 +3723,32 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.6</v>
+      <c r="Q38" s="8" t="n">
+        <v>56.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>27.3</v>
+        <v>48.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>828.7</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>28.8</v>
+        <v>24.8</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3774,28 +3767,28 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332</v>
-      </c>
-      <c r="D39" s="11" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3813,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>30.7</v>
@@ -3825,7 +3818,7 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6685.3</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
@@ -3836,8 +3829,8 @@
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>17.8</v>
+      <c r="X39" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
@@ -3859,28 +3852,28 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>2728.1</v>
+      </c>
+      <c r="D40" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>29</v>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3891,8 +3884,8 @@
       <c r="M40" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>24.6</v>
+      <c r="N40" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
@@ -3901,10 +3894,10 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>80.7</v>
+        <v>30.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
@@ -3913,7 +3906,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28</v>
@@ -3928,7 +3921,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1811.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3944,18 +3937,18 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>248.6</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>242.6</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3968,7 +3961,7 @@
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>20.9</v>
@@ -3985,17 +3978,17 @@
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="R41" s="8" t="n">
+      <c r="Q41" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>80.5</v>
+        <v>20.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
@@ -4010,9 +4003,11 @@
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -4029,26 +4024,26 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -4056,8 +4051,8 @@
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="3" t="n">
-        <v>21.2</v>
+      <c r="M42" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
@@ -4066,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>18</v>
+        <v>80.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>30.9</v>
@@ -4089,11 +4084,11 @@
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>8953.5</v>
+      <c r="X42" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>16.5</v>
@@ -4112,25 +4107,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>41.6</v>
+      <c r="I43" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4151,7 +4146,7 @@
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4175,10 +4170,10 @@
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1849.5</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>0.6</v>
@@ -4199,9 +4194,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4238,48 +4233,48 @@
       <c r="C45" s="3" t="n">
         <v>1423.4</v>
       </c>
-      <c r="D45" s="25" t="n">
-        <v>922.7</v>
-      </c>
-      <c r="E45" s="25" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="F45" s="25" t="n">
-        <v>10101.1</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>1210.1</v>
+      <c r="D45" s="24" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="F45" s="24" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>19.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>82.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>164.9</v>
+        <v>1814.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>100900160.4</v>
+        <v>105081.6</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>16128.5</v>
+        <v>1820.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>4916</v>
+        <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
+        <v>16.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1246.3</v>
+        <v>846.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>122.2</v>
+        <v>63.3</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>13.8</v>
@@ -4291,19 +4286,19 @@
         <v>66.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>222</v>
+        <v>34</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>1412.4</v>
+        <v>112.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>122.5</v>
+        <v>12.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>3983.1</v>
+        <v>9929.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>10820.9</v>
+        <v>80.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4321,20 +4316,20 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4343,13 +4338,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
@@ -4360,35 +4355,35 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>29.9</v>
+      <c r="Q46" s="8" t="n">
+        <v>95.3</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S46" s="8" t="n">
-        <v>71.7</v>
+      <c r="S46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V46" s="8" t="n">
+      <c r="U46" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V46" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>73.8</v>
+      <c r="W46" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>128.5</v>
+        <v>28.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,9 +152,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -167,19 +170,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -831,52 +831,54 @@
       <c r="J4" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Q4" s="8" t="n">
+      <c r="N4" s="9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S4" s="8" t="n">
+      <c r="R4" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="S4" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="T4" s="3" t="n">
+      <c r="T4" s="9" t="n">
         <v>56.1</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="U4" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="X4" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>7.7</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -914,52 +916,52 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="N5" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="S5" s="9" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="X5" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="9" t="n">
         <v>2.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -999,53 +1001,53 @@
       <c r="J6" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>972</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+      <c r="N6" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="S6" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>19.4</v>
+      <c r="X6" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1084,52 +1086,52 @@
       <c r="J7" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+      <c r="N7" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S7" s="3" t="n">
+      <c r="R7" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="S7" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="9" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="X7" s="8" t="n">
+      <c r="W7" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X7" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="Y7" s="9" t="n">
         <v>73.2</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="Z7" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1169,52 +1171,52 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q8" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V8" s="3" t="n">
+      <c r="S8" s="9" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="V8" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X8" s="8" t="n">
+      <c r="W8" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X8" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y8" s="9" t="n">
         <v>74.2</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" s="9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1254,14 +1256,14 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="3" t="n">
-        <v>108</v>
+      <c r="M9" s="9" t="n">
+        <v>109</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>12.8</v>
@@ -1272,10 +1274,10 @@
       <c r="P9" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>8556.6</v>
-      </c>
-      <c r="R9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="R9" s="9" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1287,10 +1289,10 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="W9" s="3" t="n">
+      <c r="V9" s="9" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="W9" s="9" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1342,13 +1344,13 @@
       <c r="K10" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="M10" s="3" t="n">
+      <c r="L10" s="9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M10" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1357,35 +1359,35 @@
       <c r="P10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="3" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V10" s="3" t="n">
+      <c r="S10" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>877.8</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>18.4</v>
+      <c r="X10" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1417,7 @@
       <c r="G11" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="17" t="n">
         <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
@@ -1424,53 +1426,53 @@
       <c r="J11" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="P11" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>256.3</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" s="3" t="n">
+      <c r="S11" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="V11" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>25.1</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>112.2</v>
+      <c r="X11" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>9.4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1512,50 +1514,50 @@
       <c r="K12" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="9" t="n">
         <v>97</v>
       </c>
-      <c r="P12" s="3" t="n">
+      <c r="P12" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S12" s="3" t="n">
+      <c r="R12" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S12" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="T12" s="3" t="n">
+      <c r="T12" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>713.2</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+      <c r="X12" s="9" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1597,49 +1599,49 @@
       <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+      <c r="N13" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q13" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S13" s="3" t="n">
+      <c r="R13" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="S13" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="T13" s="3" t="n">
+      <c r="T13" s="9" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="U13" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X13" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="9" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="9" t="n">
         <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1670,7 +1672,7 @@
       <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="17" t="n">
         <v>87.8</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1682,50 +1684,50 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+      <c r="N14" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q14" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S14" s="3" t="n">
+      <c r="R14" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S14" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="9" t="n">
         <v>77.8</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="U14" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>0</v>
+      <c r="X14" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1767,49 +1769,49 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="N15" s="9" t="n">
         <v>22.4</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P15" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S15" s="3" t="n">
+      <c r="R15" s="9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S15" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="X15" s="3" t="n">
+      <c r="W15" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X15" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="9" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="Z15" s="9" t="n">
         <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1849,14 +1851,14 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="22" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10.1</v>
+      <c r="L16" s="9" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>101.9</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>111.9</v>
@@ -1867,11 +1869,11 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="3" t="n">
-        <v>25.7</v>
+      <c r="R16" s="9" t="n">
+        <v>118.9</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>14.2</v>
@@ -1882,11 +1884,11 @@
       <c r="U16" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>212</v>
+      <c r="V16" s="9" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>118.1</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
@@ -1937,50 +1939,50 @@
       <c r="K17" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
+      <c r="N17" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>1966.2</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
+      <c r="S17" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V17" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>772.2</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>18.5</v>
+      <c r="X17" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>6.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2019,52 +2021,52 @@
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="9" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N18" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="9" t="n">
         <v>97</v>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="P18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S18" s="3" t="n">
+      <c r="R18" s="9" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="T18" s="3" t="n">
+      <c r="T18" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="3" t="n">
+      <c r="U18" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X18" s="3" t="n">
+      <c r="W18" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="X18" s="9" t="n">
         <v>29.8</v>
       </c>
-      <c r="Y18" s="3" t="n">
+      <c r="Y18" s="9" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="Z18" s="3" t="n">
+      <c r="Z18" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2104,7 +2106,7 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -2122,34 +2124,34 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="3" t="n">
+      <c r="U19" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X19" s="3" t="n">
+      <c r="W19" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X19" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="Y19" s="3" t="n">
+      <c r="Y19" s="9" t="n">
         <v>88.5</v>
       </c>
-      <c r="Z19" s="3" t="n">
+      <c r="Z19" s="9" t="n">
         <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2180,7 +2182,7 @@
       <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="17" t="n">
         <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
@@ -2189,52 +2191,52 @@
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N20" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O20" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="P20" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="S20" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="9" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="U20" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X20" s="3" t="n">
+      <c r="W20" s="9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X20" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="Y20" s="3" t="n">
+      <c r="Y20" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="Z20" s="3" t="n">
+      <c r="Z20" s="9" t="n">
         <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2274,13 +2276,13 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="17" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="16" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2292,34 +2294,34 @@
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="9" t="n">
         <v>63.1</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="U21" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X21" s="3" t="n">
+      <c r="W21" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X21" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y21" s="3" t="n">
+      <c r="Y21" s="9" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="9" t="n">
         <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2350,7 +2352,7 @@
       <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="17" t="n">
         <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2359,28 +2361,28 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="8" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="M22" s="3" t="n">
+      <c r="L22" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="M22" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="N22" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2392,19 +2394,19 @@
       <c r="U22" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X22" s="3" t="n">
+      <c r="W22" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="X22" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="Y22" s="3" t="n">
+      <c r="Y22" s="9" t="n">
         <v>88.8</v>
       </c>
-      <c r="Z22" s="3" t="n">
+      <c r="Z22" s="9" t="n">
         <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2444,13 +2446,13 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="22" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="22" t="n">
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2462,10 +2464,10 @@
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="22" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2477,11 +2479,11 @@
       <c r="U23" s="3" t="n">
         <v>795.1</v>
       </c>
-      <c r="V23" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>118.2</v>
+      <c r="V23" s="9" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>114.9</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>141.5</v>
@@ -2530,10 +2532,10 @@
       <c r="K24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="22" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="22" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2545,10 +2547,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="22" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2560,20 +2562,20 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+      <c r="X24" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>3.9</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2615,11 +2617,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="8" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>494.4</v>
+      <c r="L25" s="16" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>49.44</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2633,7 +2635,7 @@
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2645,10 +2647,10 @@
       <c r="U25" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="17" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2688,7 +2690,7 @@
       <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="17" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2713,10 +2715,10 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="16" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2728,19 +2730,19 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="X26" s="3" t="n">
+      <c r="W26" s="9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="X26" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="Y26" s="3" t="n">
+      <c r="Y26" s="9" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z26" s="3" t="n">
+      <c r="Z26" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2771,7 +2773,7 @@
       <c r="G27" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="17" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
@@ -2783,43 +2785,43 @@
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="O27" s="3" t="n">
+      <c r="O27" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P27" s="3" t="n">
+      <c r="P27" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="9" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S27" s="3" t="n">
+      <c r="R27" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="S27" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="T27" s="3" t="n">
+      <c r="T27" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="U27" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>655.1</v>
-      </c>
-      <c r="X27" s="8" t="n">
+      <c r="W27" s="16" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="X27" s="17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2856,7 +2858,7 @@
       <c r="G28" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="17" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2883,22 +2885,22 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S28" s="3" t="n">
+      <c r="R28" s="9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S28" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="T28" s="3" t="n">
+      <c r="T28" s="9" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="U28" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2950,26 +2952,26 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="9" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="M29" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="O29" s="9" t="n">
         <v>96.5</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="P29" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2978,22 +2980,22 @@
       <c r="T29" s="3" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="8" t="n">
+      <c r="U29" s="17" t="n">
         <v>7.3</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X29" s="3" t="n">
+      <c r="W29" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X29" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="Y29" s="3" t="n">
+      <c r="Y29" s="9" t="n">
         <v>81.8</v>
       </c>
-      <c r="Z29" s="3" t="n">
+      <c r="Z29" s="9" t="n">
         <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -3031,13 +3033,13 @@
       <c r="J30" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="22" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="22" t="n">
         <v>2.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="22" t="n">
         <v>10.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3049,11 +3051,11 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="22" t="n">
         <v>75.5</v>
       </c>
-      <c r="R30" s="3" t="n">
-        <v>122</v>
+      <c r="R30" s="9" t="n">
+        <v>116.5</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>183.5</v>
@@ -3064,10 +3066,10 @@
       <c r="U30" s="3" t="n">
         <v>68.8</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="22" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3115,25 +3117,25 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="O31" s="9" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="22" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3142,16 +3144,16 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
+      <c r="U31" s="17" t="n">
         <v>13.8</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="22" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="17" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
@@ -3200,49 +3202,49 @@
       <c r="K32" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="O32" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P32" s="3" t="n">
+      <c r="O32" s="9" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P32" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="3" t="n">
+      <c r="Q32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S32" s="3" t="n">
+      <c r="R32" s="9" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="S32" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="T32" s="3" t="n">
+      <c r="T32" s="9" t="n">
         <v>69.8</v>
       </c>
-      <c r="U32" s="3" t="n">
+      <c r="U32" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X32" s="3" t="n">
+      <c r="W32" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X32" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="Y32" s="3" t="n">
+      <c r="Y32" s="9" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="Z32" s="3" t="n">
+      <c r="Z32" s="9" t="n">
         <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3282,52 +3284,52 @@
       <c r="J33" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="K33" s="8" t="n">
+      <c r="K33" s="17" t="n">
         <v>22.5</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="3" t="n">
+      <c r="N33" s="9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P33" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S33" s="3" t="n">
+      <c r="R33" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S33" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="T33" s="3" t="n">
+      <c r="T33" s="9" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="U33" s="3" t="n">
+      <c r="U33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X33" s="3" t="n">
+      <c r="W33" s="9" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="X33" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="Y33" s="3" t="n">
+      <c r="Y33" s="9" t="n">
         <v>91.8</v>
       </c>
-      <c r="Z33" s="3" t="n">
+      <c r="Z33" s="9" t="n">
         <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3358,7 +3360,7 @@
       <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="17" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3370,49 +3372,49 @@
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M34" s="3" t="n">
+      <c r="M34" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="3" t="n">
+      <c r="N34" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="O34" s="3" t="n">
+      <c r="O34" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S34" s="3" t="n">
+      <c r="R34" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="S34" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="T34" s="3" t="n">
+      <c r="T34" s="9" t="n">
         <v>70.2</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="X34" s="3" t="n">
+      <c r="W34" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X34" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="Y34" s="3" t="n">
+      <c r="Y34" s="9" t="n">
         <v>62.5</v>
       </c>
-      <c r="Z34" s="3" t="n">
+      <c r="Z34" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3443,7 +3445,7 @@
       <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="17" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3455,13 +3457,13 @@
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N35" s="8" t="n">
+      <c r="M35" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="N35" s="17" t="n">
         <v>14.9</v>
       </c>
       <c r="O35" s="3" t="n">
@@ -3473,7 +3475,7 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3485,13 +3487,13 @@
       <c r="U35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="17" t="n">
         <v>95.3</v>
       </c>
       <c r="Y35" s="3" t="n">
@@ -3528,7 +3530,7 @@
       <c r="G36" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="17" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3540,25 +3542,25 @@
       <c r="K36" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="9" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P36" s="3" t="n">
+      <c r="N36" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="P36" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3568,10 +3570,10 @@
         <v>94.8</v>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="16" t="n">
         <v>61.8</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3620,14 +3622,14 @@
       <c r="J37" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="22" t="n">
         <v>1807.9</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>22.9</v>
+      <c r="M37" s="9" t="n">
+        <v>103</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>20.2</v>
@@ -3638,11 +3640,11 @@
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="22" t="n">
         <v>133.8</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>117.2</v>
+      <c r="R37" s="9" t="n">
+        <v>113.8</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>13.6</v>
@@ -3653,10 +3655,10 @@
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V37" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="W37" s="3" t="n">
+      <c r="V37" s="9" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="W37" s="22" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3708,25 +3710,25 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="N38" s="3" t="n">
+      <c r="M38" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N38" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="O38" s="3" t="n">
+      <c r="O38" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P38" s="3" t="n">
+      <c r="P38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="22" t="n">
         <v>56.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3738,10 +3740,10 @@
       <c r="U38" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="22" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3793,49 +3795,49 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P39" s="3" t="n">
+      <c r="N39" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="P39" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S39" s="3" t="n">
+      <c r="R39" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="S39" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="T39" s="3" t="n">
+      <c r="T39" s="9" t="n">
         <v>66.5</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="U39" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="X39" s="3" t="n">
+      <c r="W39" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X39" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="Y39" s="3" t="n">
+      <c r="Y39" s="9" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="Z39" s="3" t="n">
+      <c r="Z39" s="9" t="n">
         <v>10.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3878,50 +3880,50 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="N40" s="8" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P40" s="3" t="n">
+      <c r="N40" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P40" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S40" s="3" t="n">
+      <c r="R40" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="9" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="U40" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+      <c r="X40" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3963,25 +3965,25 @@
       <c r="K41" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N41" s="3" t="n">
+      <c r="M41" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N41" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O41" s="9" t="n">
         <v>93.8</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="P41" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3993,20 +3995,20 @@
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="9" t="n">
         <v>24.5</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>16.7</v>
+      <c r="X41" s="9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4048,10 +4050,10 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="17" t="n">
         <v>81.2</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4063,35 +4065,35 @@
       <c r="P42" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S42" s="3" t="n">
+      <c r="R42" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S42" s="9" t="n">
         <v>27.6</v>
       </c>
-      <c r="T42" s="3" t="n">
+      <c r="T42" s="9" t="n">
         <v>62</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>16.5</v>
+      <c r="X42" s="9" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="Y42" s="9" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="Z42" s="9" t="n">
+        <v>4.9</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4133,25 +4135,25 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P43" s="3" t="n">
+      <c r="N43" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="P43" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>21.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4163,20 +4165,20 @@
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="3" t="n">
-        <v>85.40000000000001</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>0.6</v>
+      <c r="X43" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="Y43" s="9" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="Z43" s="9" t="n">
+        <v>3.4</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4196,24 +4198,24 @@
       </c>
       <c r="D44" s="9" t="inlineStr"/>
       <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4233,13 +4235,13 @@
       <c r="C45" s="3" t="n">
         <v>1423.4</v>
       </c>
-      <c r="D45" s="24" t="n">
+      <c r="D45" s="22" t="n">
         <v>22.7</v>
       </c>
-      <c r="E45" s="24" t="n">
+      <c r="E45" s="22" t="n">
         <v>102.7</v>
       </c>
-      <c r="F45" s="24" t="n">
+      <c r="F45" s="22" t="n">
         <v>124.5</v>
       </c>
       <c r="G45" s="16" t="n">
@@ -4254,13 +4256,13 @@
       <c r="J45" s="3" t="n">
         <v>1814.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="22" t="n">
         <v>105081.6</v>
       </c>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="3" t="n">
         <v>1820.5</v>
       </c>
@@ -4270,10 +4272,10 @@
       <c r="P45" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="22" t="n">
         <v>846.3</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="22" t="n">
         <v>63.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4285,10 +4287,10 @@
       <c r="U45" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="22" t="n">
         <v>34</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="22" t="n">
         <v>112.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4325,10 +4327,10 @@
       <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="17" t="n">
         <v>9.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="17" t="n">
         <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
@@ -4340,25 +4342,25 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="O46" s="3" t="n">
+      <c r="O46" s="9" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P46" s="3" t="n">
+      <c r="P46" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="Q46" s="22" t="n">
         <v>95.3</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4370,20 +4372,20 @@
       <c r="U46" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>7.7</v>
+      <c r="X46" s="9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -47,26 +47,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -167,31 +161,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,7 +796,7 @@
         <v>351.3</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>22.7</v>
@@ -829,9 +814,9 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
@@ -841,13 +826,13 @@
         <v>22.7</v>
       </c>
       <c r="N4" s="9" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>98.2</v>
+        <v>97.5</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>33</v>
@@ -868,16 +853,16 @@
         <v>28.6</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="X4" s="9" t="n">
-        <v>31.5</v>
+        <v>29.1</v>
       </c>
       <c r="Y4" s="9" t="n">
-        <v>80.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="Z4" s="9" t="n">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -916,23 +901,23 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="O5" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="P5" s="9" t="n">
-        <v>-1.3</v>
+      <c r="M5" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q5" s="9" t="n">
         <v>26</v>
@@ -953,16 +938,16 @@
         <v>22</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="X5" s="9" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>92</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z5" s="9" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -978,7 +963,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>31.4</v>
@@ -989,8 +974,8 @@
       <c r="F6" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>20.3</v>
+      <c r="G6" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -999,9 +984,9 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="9" t="n">
@@ -1011,43 +996,43 @@
         <v>21.3</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.2</v>
+        <v>97.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>31.4</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>31.5</v>
+        <v>27.3</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>68.5</v>
+        <v>59.6</v>
       </c>
       <c r="U6" s="9" t="n">
-        <v>14.5</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>28.3</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="X6" s="9" t="n">
-        <v>31.3</v>
+        <v>29</v>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>81.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="9" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1063,7 +1048,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8218.200000000001</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>32.4</v>
@@ -1078,16 +1063,16 @@
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>21.1</v>
@@ -1096,13 +1081,13 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>98.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>31.9</v>
@@ -1148,13 +1133,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
+        <v>2368</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>33.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>27.5</v>
@@ -1166,12 +1151,12 @@
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
@@ -1181,43 +1166,43 @@
         <v>21.7</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>97.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>25.6</v>
+        <v>22.9</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>32.8</v>
+        <v>27.9</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>64.09999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>18.4</v>
+        <v>23</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>28.1</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>28.2</v>
+        <v>30.6</v>
       </c>
       <c r="Y8" s="9" t="n">
-        <v>74.2</v>
+        <v>80.3</v>
       </c>
       <c r="Z8" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1233,7 +1218,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783</v>
+        <v>1783.6</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>161.7</v>
@@ -1244,8 +1229,8 @@
       <c r="F9" s="9" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>5.4</v>
+      <c r="G9" s="9" t="n">
+        <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>100.8</v>
@@ -1256,32 +1241,32 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="16" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="9" t="n">
-        <v>109</v>
+      <c r="M9" s="16" t="n">
+        <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>12.8</v>
+        <v>128.2</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" s="9" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="16" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.5</v>
+        <v>137.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1292,17 +1277,17 @@
       <c r="V9" s="9" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="X9" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>389.1</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+      <c r="X9" s="9" t="n">
+        <v>2087.1</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>1320</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1318,7 +1303,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>256.7</v>
+        <v>356.7</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>32.3</v>
@@ -1333,36 +1318,36 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L10" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="16" t="n">
         <v>21.6</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="16" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="9" t="n">
@@ -1377,7 +1362,7 @@
       <c r="V10" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="16" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="9" t="n">
@@ -1414,20 +1399,20 @@
       <c r="F11" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>18.7</v>
+      <c r="G11" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>18.1</v>
+        <v>14.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>20.6</v>
@@ -1448,31 +1433,31 @@
         <v>33.2</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>25.8</v>
+        <v>23.2</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>33.2</v>
+        <v>28.5</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>65.2</v>
+        <v>56.3</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>17.7</v>
+        <v>22.1</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>29.5</v>
       </c>
       <c r="W11" s="9" t="n">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
       <c r="X11" s="9" t="n">
-        <v>31.9</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>77.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>9.4</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1488,7 +1473,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1218.2</v>
+        <v>2418.2</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>32.8</v>
@@ -1502,16 +1487,16 @@
       <c r="G12" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="9" t="n">
@@ -1547,17 +1532,17 @@
       <c r="V12" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="9" t="n">
+      <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>8.699999999999999</v>
+      <c r="X12" s="18" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>173.2</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1573,13 +1558,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>238.1</v>
+        <v>230.1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>24.9</v>
@@ -1591,12 +1576,12 @@
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="L13" s="9" t="n">
@@ -1632,17 +1617,17 @@
       <c r="V13" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X13" s="9" t="n">
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>6.6</v>
+      <c r="Z13" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1658,22 +1643,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1221.4</v>
+        <v>121.4</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="17" t="n">
-        <v>87.8</v>
+      <c r="H14" s="18" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
@@ -1681,7 +1666,7 @@
       <c r="J14" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
@@ -1717,17 +1702,17 @@
       <c r="V14" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="9" t="n">
+      <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>3.8</v>
+      <c r="X14" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1743,16 +1728,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>340.8</v>
+        <v>2340.8</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>12.1</v>
@@ -1764,9 +1749,9 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
@@ -1828,22 +1813,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>15308.1</v>
+        <v>1530.8</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>154.2</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="G16" s="3" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>1192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1851,7 +1836,7 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="L16" s="9" t="n">
@@ -1860,35 +1845,35 @@
       <c r="M16" s="9" t="n">
         <v>101.9</v>
       </c>
-      <c r="N16" s="3" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>490</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>2.2</v>
+      <c r="N16" s="9" t="n">
+        <v>1122.4</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>41.1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="9" t="n">
-        <v>118.9</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>7.6</v>
+      <c r="R16" s="16" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>2505.6</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>2993</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>118.1</v>
+      <c r="W16" s="16" t="n">
+        <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
@@ -1897,7 +1882,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>142.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1913,18 +1898,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
+        <v>230.6</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>30.4</v>
+        <v>30.8</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G17" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1937,7 +1922,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>20.6</v>
@@ -1957,7 +1942,7 @@
       <c r="Q17" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="16" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="9" t="n">
@@ -1972,17 +1957,17 @@
       <c r="V17" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="16" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>6.3</v>
+      <c r="X17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1998,10 +1983,10 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3341.1</v>
+        <v>33.2</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>19.2</v>
@@ -2013,13 +1998,13 @@
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
@@ -2028,16 +2013,16 @@
         <v>19.7</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N18" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N18" s="18" t="n">
         <v>22.3</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P18" s="9" t="n">
-        <v>0.7</v>
+      <c r="P18" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="Q18" s="9" t="n">
         <v>32.2</v>
@@ -2058,16 +2043,16 @@
         <v>28.3</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X18" s="9" t="n">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>77.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="Z18" s="9" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2068,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
+        <v>32.6</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>32.2</v>
@@ -2109,19 +2094,19 @@
       <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="O19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="O19" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P19" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="Q19" s="9" t="n">
@@ -2182,8 +2167,8 @@
       <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="17" t="n">
-        <v>18.4</v>
+      <c r="H20" s="18" t="n">
+        <v>118.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2198,7 +2183,7 @@
         <v>19.8</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N20" s="9" t="n">
         <v>22.8</v>
@@ -2253,13 +2238,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
+        <v>35.7</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>30.1</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>24.1</v>
@@ -2267,7 +2252,7 @@
       <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="18" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2279,19 +2264,19 @@
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="16" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="N21" s="3" t="n">
+      <c r="M21" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
@@ -2313,16 +2298,16 @@
         <v>26.3</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="X21" s="9" t="n">
-        <v>28.8</v>
+        <v>30.2</v>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>84.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="Z21" s="9" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2338,7 +2323,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1492.9</v>
+        <v>294.9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>31.2</v>
@@ -2352,8 +2337,8 @@
       <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H22" s="17" t="n">
-        <v>17.4</v>
+      <c r="H22" s="18" t="n">
+        <v>167.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
@@ -2379,35 +2364,35 @@
       <c r="P22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>21</v>
+      <c r="Q22" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="R22" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>4.8</v>
+      <c r="S22" s="9" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>11.7</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>24</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="X22" s="9" t="n">
-        <v>26.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y22" s="9" t="n">
-        <v>88.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Z22" s="9" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2423,22 +2408,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
+        <v>161</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>155.4</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>125.8</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="9" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.8</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2449,14 +2434,14 @@
       <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="L23" s="9" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="22" t="n">
-        <v>97.8</v>
+      <c r="M23" s="9" t="n">
+        <v>98</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>12.2</v>
+        <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2464,35 +2449,35 @@
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="22" t="n">
+      <c r="Q23" s="9" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="16" t="n">
         <v>124.6</v>
       </c>
-      <c r="S23" s="3" t="n">
-        <v>1139.7</v>
-      </c>
-      <c r="T23" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="U23" s="3" t="n">
-        <v>795.1</v>
+      <c r="S23" s="9" t="n">
+        <v>2419.8</v>
+      </c>
+      <c r="T23" s="9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>3154.6</v>
       </c>
       <c r="V23" s="9" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="9" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="Y23" s="3" t="n">
-        <v>422</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+      <c r="W23" s="16" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="X23" s="9" t="n">
+        <v>2013.5</v>
+      </c>
+      <c r="Y23" s="9" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z23" s="9" t="n">
+        <v>790.6</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2508,7 +2493,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>380.3</v>
+        <v>322</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>31.1</v>
@@ -2528,54 +2513,56 @@
       <c r="I24" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="J24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="n">
+        <v>3.7</v>
+      </c>
       <c r="K24" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L24" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="22" t="n">
+      <c r="M24" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="N24" s="3" t="n">
+      <c r="N24" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="O24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="O24" s="9" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P24" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="22" t="n">
+      <c r="Q24" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="16" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>15.9</v>
+      <c r="S24" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>12.5</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="16" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="Y24" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z24" s="9" t="n">
-        <v>3.9</v>
+      <c r="X24" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2594,10 +2581,10 @@
         <v>177.8</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>24.9</v>
@@ -2609,19 +2596,19 @@
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.4</v>
+        <v>11.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="3" t="n">
+      <c r="K25" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="16" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="M25" s="16" t="n">
-        <v>49.44</v>
+      <c r="L25" s="19" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2632,35 +2619,35 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="9" t="n">
         <v>22.9</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>1.8</v>
+      <c r="S25" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="V25" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="17" t="n">
+      <c r="W25" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+      <c r="X25" s="9" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="Y25" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z25" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2690,16 +2677,16 @@
       <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="17" t="n">
+      <c r="H26" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="K26" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
@@ -2709,25 +2696,27 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>15.8</v>
+        <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="16" t="n">
-        <v>88.40000000000001</v>
+      <c r="P26" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>31.4</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T26" s="9" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="V26" s="9" t="n">
@@ -2762,27 +2751,27 @@
         <v>418.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>37</v>
+        <v>32.9</v>
       </c>
       <c r="E27" s="9" t="n">
         <v>19.2</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="H27" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H27" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>13.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
@@ -2818,17 +2807,17 @@
       <c r="V27" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="16" t="n">
-        <v>65.51000000000001</v>
-      </c>
-      <c r="X27" s="17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>10.5</v>
+      <c r="W27" s="9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2844,21 +2833,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.3</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G28" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2867,10 +2856,10 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="18" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
@@ -2903,17 +2892,17 @@
       <c r="V28" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>0.2</v>
+      <c r="X28" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="Y28" s="9" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="Z28" s="9" t="n">
+        <v>3.1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2929,16 +2918,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>14</v>
+        <v>146.2</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>8.9</v>
@@ -2952,7 +2941,9 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="13" t="inlineStr"/>
+      <c r="K29" s="9" t="n">
+        <v>18.1</v>
+      </c>
       <c r="L29" s="9" t="n">
         <v>21.9</v>
       </c>
@@ -2968,35 +2959,35 @@
       <c r="P29" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="9" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S29" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="T29" s="9" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="17" t="n">
-        <v>7.3</v>
+      <c r="U29" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>25.9</v>
+        <v>27.4</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>81.8</v>
+        <v>86.5</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3011,39 +3002,41 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>136.3</v>
+      </c>
       <c r="D30" s="9" t="n">
-        <v>161.6</v>
+        <v>156.5</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>130.7</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>56.8</v>
+        <v>127.9</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>25.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>922.8</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K30" s="22" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="K30" s="9" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M30" s="22" t="n">
-        <v>10.1</v>
+      <c r="L30" s="16" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M30" s="16" t="n">
+        <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>111.3</v>
+        <v>117.8</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
@@ -3051,35 +3044,35 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="22" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="R30" s="9" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="U30" s="3" t="n">
-        <v>68.8</v>
+      <c r="Q30" s="9" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="R30" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>2156</v>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>2378.5</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="22" t="n">
+      <c r="W30" s="16" t="n">
         <v>115.3</v>
       </c>
-      <c r="X30" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>411.5</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+      <c r="X30" s="9" t="n">
+        <v>1787.4</v>
+      </c>
+      <c r="Y30" s="9" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>855.7</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3099,9 @@
       <c r="F31" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>11.4</v>
+      </c>
       <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
@@ -3114,53 +3109,55 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="16" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="16" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="O31" s="9" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="O31" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="22" t="n">
+      <c r="Q31" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="16" t="n">
         <v>24.2</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="U31" s="17" t="n">
-        <v>13.8</v>
+      <c r="S31" s="9" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>10.1</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="22" t="n">
+      <c r="W31" s="16" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="17" t="n">
+      <c r="X31" s="18" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3190,14 +3187,14 @@
       <c r="G32" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="18" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>2.4</v>
+        <v>12.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3212,7 +3209,7 @@
         <v>25.6</v>
       </c>
       <c r="O32" s="9" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P32" s="9" t="n">
         <v>0.2</v>
@@ -3236,16 +3233,16 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="9" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="X32" s="9" t="n">
-        <v>29.1</v>
+        <v>31.5</v>
       </c>
       <c r="Y32" s="9" t="n">
-        <v>81.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="Z32" s="9" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3261,7 +3258,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>48.1</v>
+        <v>44.1</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>25.2</v>
@@ -3279,13 +3276,13 @@
         <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K33" s="17" t="n">
-        <v>22.5</v>
+        <v>0.3</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="L33" s="9" t="n">
         <v>20.8</v>
@@ -3294,43 +3291,43 @@
         <v>20.6</v>
       </c>
       <c r="N33" s="9" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>98.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="T33" s="9" t="n">
-        <v>83.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="U33" s="9" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="V33" s="9" t="n">
         <v>23</v>
       </c>
       <c r="W33" s="9" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="X33" s="9" t="n">
-        <v>25.8</v>
+        <v>26.4</v>
       </c>
       <c r="Y33" s="9" t="n">
-        <v>91.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="Z33" s="9" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3360,14 +3357,14 @@
       <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="17" t="n">
+      <c r="H34" s="18" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
@@ -3445,7 +3442,7 @@
       <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="17" t="n">
+      <c r="H35" s="18" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3458,49 +3455,49 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>19</v>
+        <v>11.9</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N35" s="17" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O35" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="O35" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="P35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>28.3</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>9.4</v>
+      <c r="S35" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>7.2</v>
       </c>
       <c r="V35" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="3" t="n">
+      <c r="W35" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="17" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+      <c r="X35" s="9" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>3.7</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3516,7 +3513,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
+        <v>1117.2</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>28.6</v>
@@ -3528,10 +3525,10 @@
         <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>19</v>
+        <v>17.5</v>
+      </c>
+      <c r="H36" s="18" t="n">
+        <v>119</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3540,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="L36" s="9" t="n">
         <v>21.9</v>
@@ -3552,38 +3549,40 @@
         <v>25.9</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>98.5</v>
+        <v>98.8</v>
       </c>
       <c r="P36" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q36" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q36" s="9" t="n">
         <v>21.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S36" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S36" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="9" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="inlineStr"/>
+      <c r="U36" s="9" t="n">
+        <v>1.3</v>
+      </c>
       <c r="V36" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="16" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>19.3</v>
+      <c r="W36" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X36" s="9" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3610,8 +3609,8 @@
       <c r="F37" s="9" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>42.9</v>
+      <c r="G37" s="19" t="n">
+        <v>14.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3620,49 +3619,49 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K37" s="22" t="n">
-        <v>1807.9</v>
-      </c>
-      <c r="L37" s="9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K37" s="16" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L37" s="16" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>103</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q37" s="22" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="R37" s="9" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>3923.6</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>40.4</v>
+      <c r="M37" s="16" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>1163.5</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="16" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="S37" s="9" t="n">
+        <v>1948.4</v>
+      </c>
+      <c r="T37" s="9" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="U37" s="9" t="n">
+        <v>1202</v>
       </c>
       <c r="V37" s="9" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="22" t="n">
-        <v>112.2</v>
+      <c r="W37" s="9" t="n">
+        <v>110.7</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>12.2</v>
+        <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>416</v>
@@ -3684,7 +3683,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
+        <v>16.5</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>28.6</v>
@@ -3698,22 +3697,22 @@
       <c r="G38" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="18" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L38" s="16" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="16" t="n">
         <v>20.6</v>
       </c>
       <c r="N38" s="9" t="n">
@@ -3725,35 +3724,35 @@
       <c r="P38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="22" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="R38" s="9" t="n">
+      <c r="Q38" s="9" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="R38" s="16" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>81.09999999999999</v>
+      <c r="S38" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>5.7</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="22" t="n">
+      <c r="W38" s="9" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3769,7 +3768,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>33.2</v>
+        <v>332.3</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>30.7</v>
@@ -3787,58 +3786,58 @@
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K39" s="3" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="M39" s="9" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="N39" s="9" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="P39" s="9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>30.7</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>29.3</v>
+        <v>32.6</v>
       </c>
       <c r="T39" s="9" t="n">
-        <v>66.5</v>
+        <v>73.8</v>
       </c>
       <c r="U39" s="9" t="n">
-        <v>14.7</v>
+        <v>11.6</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="9" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
       <c r="X39" s="9" t="n">
-        <v>27.2</v>
+        <v>29.7</v>
       </c>
       <c r="Y39" s="9" t="n">
-        <v>72.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="Z39" s="9" t="n">
-        <v>10.1</v>
+        <v>7.7</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3854,13 +3853,13 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2728.1</v>
+        <v>278.1</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>30.8</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>20.6</v>
+        <v>20.06</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>25.7</v>
@@ -3884,13 +3883,13 @@
         <v>21</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>0.2</v>
@@ -3899,16 +3898,16 @@
         <v>30.7</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>28.8</v>
+        <v>32.2</v>
       </c>
       <c r="T40" s="9" t="n">
-        <v>65.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="U40" s="9" t="n">
-        <v>15.2</v>
+        <v>11.9</v>
       </c>
       <c r="V40" s="9" t="n">
         <v>28</v>
@@ -3957,11 +3956,9 @@
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
         <v>11.8</v>
       </c>
@@ -3980,20 +3977,20 @@
       <c r="P41" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="9" t="n">
         <v>29.3</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12</v>
+      <c r="S41" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>27.1</v>
@@ -4053,17 +4050,17 @@
       <c r="L42" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="17" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
+      <c r="M42" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="O42" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="P42" s="3" t="n">
-        <v>80.8</v>
+      <c r="P42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>30.9</v>
@@ -4120,14 +4117,14 @@
       <c r="F43" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>18.6</v>
+      <c r="G43" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>8.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4145,25 +4142,25 @@
         <v>25</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P43" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S43" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S43" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="T43" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="U43" s="3" t="n">
-        <v>2.1</v>
+      <c r="U43" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="V43" s="9" t="n">
         <v>24</v>
@@ -4198,18 +4195,18 @@
       </c>
       <c r="D44" s="9" t="inlineStr"/>
       <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="13" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
@@ -4235,72 +4232,74 @@
       <c r="C45" s="3" t="n">
         <v>1423.4</v>
       </c>
-      <c r="D45" s="22" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="F45" s="22" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="G45" s="16" t="n">
+      <c r="D45" s="9" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="G45" s="19" t="n">
         <v>19.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1814.9</v>
-      </c>
-      <c r="K45" s="22" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="K45" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="22" t="n">
-        <v>105081.6</v>
-      </c>
-      <c r="M45" s="14" t="inlineStr"/>
+      <c r="L45" s="9" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>102.4</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>1820.5</v>
+        <v>120.5</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q45" s="22" t="n">
-        <v>846.3</v>
-      </c>
-      <c r="R45" s="22" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="V45" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="W45" s="22" t="n">
-        <v>112.8</v>
+        <v>11.9</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="R45" s="16" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>2248.4</v>
+      </c>
+      <c r="T45" s="9" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>2390.2</v>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v>134</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>12.2</v>
+        <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>9929.5</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>80.5</v>
+        <v>38</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4327,11 +4326,11 @@
       <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="17" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H46" s="17" t="n">
-        <v>88.7</v>
+      <c r="G46" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4340,13 +4339,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N46" s="9" t="n">
         <v>24.1</v>
@@ -4357,11 +4356,11 @@
       <c r="P46" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="22" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>24.5</v>
+      <c r="Q46" s="9" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="16" t="n">
+        <v>23.8</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>27.8</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,31 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,7 +149,22 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,16 +780,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -816,52 +801,52 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="8" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="9" t="n">
+      <c r="P4" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>56.1</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="X4" s="9" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="Y4" s="9" t="n">
+      <c r="Y4" s="8" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z4" s="9" t="n">
+      <c r="Z4" s="8" t="n">
         <v>10</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -880,16 +865,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -901,52 +886,52 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q5" s="9" t="n">
+      <c r="M5" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="S5" s="9" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V5" s="9" t="n">
+      <c r="R5" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="9" t="n">
+      <c r="X5" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="8" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="Z5" s="9" t="n">
+      <c r="Z5" s="8" t="n">
         <v>1.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -963,18 +948,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -986,52 +971,52 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+      <c r="N6" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>59.6</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1048,18 +1033,18 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1071,52 +1056,52 @@
       <c r="J7" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+      <c r="N7" s="8" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="X7" s="9" t="n">
+      <c r="X7" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="Y7" s="9" t="n">
+      <c r="Y7" s="8" t="n">
         <v>73.2</v>
       </c>
-      <c r="Z7" s="9" t="n">
+      <c r="Z7" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1133,18 +1118,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1156,53 +1141,53 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="O8" s="9" t="n">
-        <v>96.59999999999999</v>
-      </c>
-      <c r="P8" s="9" t="n">
+      <c r="O8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>54.8</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X8" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>7.5</v>
+      <c r="W8" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z8" s="8" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1220,16 +1205,16 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>161.7</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1241,13 +1226,13 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="8" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1259,10 +1244,10 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="9" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1274,20 +1259,20 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="X9" s="9" t="n">
-        <v>2087.1</v>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="Z9" s="9" t="n">
-        <v>1320</v>
+      <c r="X9" s="3" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>389.1</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1305,20 +1290,20 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1329,49 +1314,49 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q10" s="9" t="n">
+      <c r="N10" s="8" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="S10" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="T10" s="9" t="n">
+      <c r="T10" s="8" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="U10" s="9" t="n">
+      <c r="U10" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="9" t="n">
+      <c r="X10" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="Y10" s="9" t="n">
+      <c r="Y10" s="8" t="n">
         <v>83.2</v>
       </c>
-      <c r="Z10" s="9" t="n">
+      <c r="Z10" s="8" t="n">
         <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1390,73 +1375,73 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="H11" s="18" t="n">
-        <v>88.7</v>
+      <c r="H11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="N11" s="9" t="n">
+      <c r="N11" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P11" s="9" t="n">
+      <c r="P11" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="S11" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="T11" s="9" t="n">
+      <c r="T11" s="8" t="n">
         <v>56.3</v>
       </c>
-      <c r="U11" s="9" t="n">
+      <c r="U11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1473,75 +1458,75 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="9" t="n">
+      <c r="N12" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="O12" s="9" t="n">
+      <c r="O12" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="P12" s="9" t="n">
+      <c r="P12" s="8" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="S12" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="T12" s="9" t="n">
+      <c r="T12" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="9" t="n">
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="18" t="n">
+      <c r="W12" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="X12" s="8" t="n">
         <v>30.3</v>
       </c>
-      <c r="Y12" s="3" t="n">
-        <v>173.2</v>
-      </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Y12" s="8" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="Z12" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1560,74 +1545,74 @@
       <c r="C13" s="3" t="n">
         <v>230.1</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="9" t="n">
+      <c r="N13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="O13" s="9" t="n">
+      <c r="O13" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="P13" s="9" t="n">
+      <c r="P13" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
+      <c r="W13" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="8" t="n">
         <v>80.8</v>
       </c>
-      <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+      <c r="Z13" s="8" t="n">
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1645,74 +1630,74 @@
       <c r="C14" s="3" t="n">
         <v>121.4</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="9" t="n">
+      <c r="N14" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P14" s="9" t="n">
+      <c r="P14" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="8" t="n">
         <v>77.8</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X14" s="3" t="n">
+      <c r="W14" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="X14" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="Y14" s="3" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>15</v>
+      <c r="Y14" s="8" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="Z14" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1728,18 +1713,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2340.8</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1749,54 +1734,54 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1815,20 +1800,20 @@
       <c r="C16" s="3" t="n">
         <v>1530.8</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="G16" s="9" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1836,43 +1821,43 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="8" t="n">
         <v>102.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>101.9</v>
       </c>
-      <c r="N16" s="9" t="n">
-        <v>1122.4</v>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="Q16" s="9" t="n">
+      <c r="N16" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>490</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="9" t="n">
         <v>125.7</v>
       </c>
-      <c r="S16" s="9" t="n">
-        <v>2505.6</v>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v>2993</v>
-      </c>
-      <c r="V16" s="9" t="n">
+      <c r="S16" s="3" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>331</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="9" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1882,7 +1867,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>142.3</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1898,18 +1883,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1922,52 +1907,52 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="9" t="n">
+      <c r="N17" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P17" s="9" t="n">
+      <c r="P17" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="9" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>72.90000000000001</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+      <c r="X17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y17" s="8" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="Z17" s="8" t="n">
+        <v>6.3</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1983,18 +1968,18 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D18" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -2006,53 +1991,53 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M18" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="N18" s="18" t="n">
+      <c r="M18" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N18" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O18" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+      <c r="P18" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X18" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="Y18" s="9" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="Z18" s="9" t="n">
-        <v>6.6</v>
+      <c r="W18" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="Y18" s="8" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="Z18" s="8" t="n">
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2068,18 +2053,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2091,52 +2076,52 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q19" s="9" t="n">
+      <c r="N19" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>88.5</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2155,73 +2140,73 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <v>118.4</v>
+      <c r="H20" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N20" s="9" t="n">
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="P20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2238,21 +2223,21 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="18" t="n">
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2261,53 +2246,53 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>63.1</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="9" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="X21" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="Y21" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z21" s="9" t="n">
-        <v>4</v>
+      <c r="W21" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="Y21" s="8" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Z21" s="8" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2325,74 +2310,74 @@
       <c r="C22" s="3" t="n">
         <v>294.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>167.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R22" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S22" s="9" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="U22" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="V22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X22" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y22" s="9" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="Z22" s="9" t="n">
-        <v>2.4</v>
+      <c r="S22" s="8" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Y22" s="8" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z22" s="8" t="n">
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2410,16 +2395,16 @@
       <c r="C23" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>125.8</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2431,53 +2416,53 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="9" t="n">
-        <v>98</v>
+      <c r="M23" s="8" t="n">
+        <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>94</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="9" t="n">
         <v>124.6</v>
       </c>
-      <c r="S23" s="9" t="n">
-        <v>2419.8</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="U23" s="9" t="n">
-        <v>3154.6</v>
-      </c>
-      <c r="V23" s="9" t="n">
+      <c r="S23" s="3" t="n">
+        <v>139.7</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="W23" s="9" t="n">
         <v>118.9</v>
       </c>
-      <c r="X23" s="9" t="n">
-        <v>2013.5</v>
-      </c>
-      <c r="Y23" s="9" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z23" s="9" t="n">
-        <v>790.6</v>
+      <c r="X23" s="3" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>422</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2495,16 +2480,16 @@
       <c r="C24" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2517,52 +2502,52 @@
         <v>3.7</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="N24" s="9" t="n">
+      <c r="N24" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="O24" s="9" t="n">
+      <c r="O24" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P24" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>31.5</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>71.7</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+      <c r="X24" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Y24" s="8" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z24" s="8" t="n">
+        <v>3.9</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2580,37 +2565,37 @@
       <c r="C25" s="3" t="n">
         <v>177.8</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="19" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="M25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
@@ -2619,34 +2604,34 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>95.3</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="8" t="n">
         <v>0.8</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2663,21 +2648,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>345</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2686,52 +2671,52 @@
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="N26" s="3" t="n">
+      <c r="N26" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="O26" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="P26" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="X26" s="9" t="n">
+      <c r="X26" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="Y26" s="9" t="n">
+      <c r="Y26" s="8" t="n">
         <v>74.3</v>
       </c>
-      <c r="Z26" s="9" t="n">
+      <c r="Z26" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2748,76 +2733,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="n">
+      <c r="F27" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X27" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>8.1</v>
+      <c r="W27" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>10.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2833,18 +2818,18 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2856,53 +2841,53 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="18" t="n">
+      <c r="L28" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="N28" s="3" t="n">
+      <c r="M28" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N28" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="O28" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="O28" s="8" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="P28" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X28" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>3.1</v>
+      <c r="W28" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>4.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2920,16 +2905,16 @@
       <c r="C29" s="3" t="n">
         <v>146.2</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2941,53 +2926,53 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>96.5</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="T29" s="9" t="n">
+      <c r="T29" s="8" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="9" t="n">
+      <c r="U29" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X29" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="Y29" s="9" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="Z29" s="9" t="n">
-        <v>4.3</v>
+      <c r="W29" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Y29" s="8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z29" s="8" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -3003,36 +2988,36 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>156.5</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>127.9</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>25.7</v>
+      <c r="F30" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1171.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="16" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="M30" s="16" t="n">
+      <c r="L30" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="M30" s="8" t="n">
         <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3044,35 +3029,35 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="9" t="n">
         <v>121</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>2156</v>
-      </c>
-      <c r="T30" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="U30" s="9" t="n">
-        <v>2378.5</v>
-      </c>
-      <c r="V30" s="9" t="n">
+      <c r="S30" s="3" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="9" t="n">
         <v>115.3</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>1787.4</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>855.7</v>
+      <c r="X30" s="3" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3090,16 +3075,16 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3109,55 +3094,55 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="3" t="n">
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="P31" s="3" t="n">
+      <c r="O31" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P31" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>30.2</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="18" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+      <c r="X31" s="8" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>4.4</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3175,74 +3160,74 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="18" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="S32" s="9" t="n">
+      <c r="S32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="T32" s="9" t="n">
+      <c r="T32" s="8" t="n">
         <v>69.8</v>
       </c>
-      <c r="U32" s="9" t="n">
+      <c r="U32" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X32" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="Y32" s="9" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="Z32" s="9" t="n">
-        <v>4.4</v>
+      <c r="W32" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Y32" s="8" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z32" s="8" t="n">
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3260,16 +3245,16 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3281,52 +3266,52 @@
       <c r="J33" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L33" s="9" t="n">
+      <c r="K33" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="9" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V33" s="9" t="n">
+      <c r="R33" s="8" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>1.7</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3345,73 +3330,73 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="18" t="n">
+      <c r="H34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="S34" s="9" t="n">
+      <c r="S34" s="8" t="n">
         <v>29.9</v>
       </c>
-      <c r="T34" s="9" t="n">
+      <c r="T34" s="8" t="n">
         <v>70.2</v>
       </c>
-      <c r="U34" s="9" t="n">
+      <c r="U34" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>62.5</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3430,19 +3415,19 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="18" t="n">
+      <c r="H35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3451,53 +3436,53 @@
       <c r="J35" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N35" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="O35" s="9" t="n">
+      <c r="L35" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="O35" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S35" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V35" s="9" t="n">
+      <c r="R35" s="8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V35" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X35" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="Y35" s="9" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="Z35" s="9" t="n">
-        <v>3.7</v>
+      <c r="W35" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y35" s="8" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="Z35" s="8" t="n">
+        <v>4.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3513,22 +3498,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="9" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H36" s="18" t="n">
-        <v>119</v>
+      <c r="G36" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3536,53 +3521,53 @@
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="8" t="n">
         <v>98.8</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="S36" s="9" t="n">
+      <c r="S36" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="T36" s="9" t="n">
+      <c r="T36" s="8" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="9" t="n">
+      <c r="U36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X36" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="Y36" s="9" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="Z36" s="9" t="n">
-        <v>0.9</v>
+      <c r="W36" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Y36" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="Z36" s="8" t="n">
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3600,17 +3585,17 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="19" t="n">
-        <v>14.3</v>
+      <c r="G37" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3621,50 +3606,50 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="16" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="16" t="n">
+      <c r="M37" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="N37" s="9" t="n">
-        <v>1163.5</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P37" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+      <c r="N37" s="3" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="16" t="n">
+      <c r="R37" s="9" t="n">
         <v>117.9</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>1948.4</v>
-      </c>
-      <c r="T37" s="9" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="V37" s="9" t="n">
+      <c r="S37" s="3" t="n">
+        <v>136.3</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>393.6</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>110.7</v>
+        <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>16</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3683,21 +3668,21 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="18" t="n">
+      <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
@@ -3707,52 +3692,52 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="16" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="9" t="n">
+      <c r="S38" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="T38" s="9" t="n">
+      <c r="T38" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="U38" s="9" t="n">
+      <c r="U38" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="X38" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+      <c r="X38" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="Y38" s="8" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Z38" s="8" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3768,75 +3753,75 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S39" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="T39" s="9" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="V39" s="9" t="n">
+      <c r="R39" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>79.3</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>7.7</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3855,23 +3840,23 @@
       <c r="C40" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.1</v>
@@ -3879,49 +3864,49 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M40" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N40" s="9" t="n">
+      <c r="M40" s="8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S40" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="T40" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V40" s="9" t="n">
+      <c r="R40" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>29.8</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3940,72 +3925,72 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L41" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="8" t="n">
         <v>23.2</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="8" t="n">
         <v>93.8</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S41" s="9" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="T41" s="9" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="U41" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="V41" s="9" t="n">
+      <c r="R41" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="9" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="Y41" s="9" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="Z41" s="9" t="n">
-        <v>5.1</v>
+      <c r="W41" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="Y41" s="8" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z41" s="8" t="n">
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4023,23 +4008,23 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
@@ -4047,50 +4032,50 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="9" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="X42" s="9" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="Y42" s="9" t="n">
-        <v>86.2</v>
-      </c>
-      <c r="Z42" s="9" t="n">
-        <v>4.9</v>
+      <c r="W42" s="8" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="8" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="Z42" s="8" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4108,23 +4093,23 @@
       <c r="C43" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="18" t="n">
-        <v>8.6</v>
+      <c r="G43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4132,49 +4117,49 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="9" t="n">
+      <c r="N43" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="8" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="P43" s="9" t="n">
+      <c r="P43" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q43" s="9" t="n">
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="S43" s="9" t="n">
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="T43" s="9" t="n">
+      <c r="T43" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="U43" s="9" t="n">
+      <c r="U43" s="8" t="n">
         <v>7.1</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="9" t="n">
+      <c r="X43" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="Y43" s="9" t="n">
+      <c r="Y43" s="8" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="Z43" s="9" t="n">
+      <c r="Z43" s="8" t="n">
         <v>3.4</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4193,26 +4178,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="14" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="14" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="14" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4230,19 +4215,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1423.4</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>152.7</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="E45" s="8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="G45" s="19" t="n">
-        <v>19.1</v>
+      <c r="G45" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
@@ -4251,16 +4236,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="K45" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="9" t="n">
-        <v>102.4</v>
+      <c r="M45" s="8" t="n">
+        <v>102.5</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>120.5</v>
@@ -4269,24 +4254,24 @@
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="16" t="n">
+      <c r="R45" s="9" t="n">
         <v>122.3</v>
       </c>
-      <c r="S45" s="9" t="n">
-        <v>2248.4</v>
-      </c>
-      <c r="T45" s="9" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v>2390.2</v>
-      </c>
-      <c r="V45" s="9" t="n">
+      <c r="S45" s="3" t="n">
+        <v>138.4</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
       <c r="W45" s="9" t="n">
@@ -4296,7 +4281,7 @@
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>392.3</v>
+        <v>92.3</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>38</v>
@@ -4317,73 +4302,73 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="P46" s="9" t="n">
+      <c r="P46" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="V46" s="9" t="n">
+      <c r="R46" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>32.4</v>
@@ -1247,7 +1247,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="R9" s="16" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1262,7 +1262,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="16" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1303,7 +1303,7 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1312,7 +1312,7 @@
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>21.9</v>
@@ -1332,7 +1332,7 @@
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="16" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1347,7 +1347,7 @@
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="16" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
@@ -1394,7 +1394,7 @@
         <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>32.8</v>
@@ -1803,7 +1803,7 @@
       <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="16" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="F16" s="8" t="n">
@@ -1842,7 +1842,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="16" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1857,7 +1857,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="9" t="n">
+      <c r="W16" s="16" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1927,7 +1927,7 @@
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="16" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1942,7 +1942,7 @@
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="16" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2229,7 +2229,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2319,8 +2319,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.9</v>
+      <c r="G22" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2398,7 +2398,7 @@
       <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="16" t="n">
         <v>96.2</v>
       </c>
       <c r="F23" s="8" t="n">
@@ -2429,7 +2429,7 @@
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
@@ -2437,7 +2437,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="16" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2452,7 +2452,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="16" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2522,7 +2522,7 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="16" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
@@ -2537,7 +2537,7 @@
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="9" t="n">
+      <c r="W24" s="16" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>32.9</v>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>28.2</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3032,7 +3032,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="16" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,14 +3047,14 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="16" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3097,7 +3097,7 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>20.4</v>
@@ -3117,7 +3117,7 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="16" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3132,7 +3132,7 @@
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="16" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3440,13 +3440,13 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>100</v>
@@ -3609,10 +3609,10 @@
       <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3627,7 +3627,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="16" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3642,14 +3642,14 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="16" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3712,7 +3712,7 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="16" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3727,7 +3727,7 @@
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="16" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3774,7 +3774,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -3868,7 +3868,7 @@
         <v>21</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N40" s="8" t="n">
         <v>24.6</v>
@@ -4238,14 +4238,14 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="16" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
       <c r="M45" s="8" t="n">
-        <v>102.5</v>
+        <v>102.6</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>120.5</v>
@@ -4259,7 +4259,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="16" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4274,17 +4274,17 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="16" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>92.3</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>
@@ -4344,7 +4344,7 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="9" t="n">
+      <c r="R46" s="16" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
@@ -4359,7 +4359,7 @@
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="16" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -161,10 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1247,7 +1244,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="15" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1262,7 +1259,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="16" t="n">
+      <c r="W9" s="15" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1332,7 +1329,7 @@
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="15" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1347,7 +1344,7 @@
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="16" t="n">
+      <c r="W10" s="15" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
@@ -1373,13 +1370,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>26.6</v>
@@ -1803,13 +1800,13 @@
       <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="16" t="n">
-        <v>99.40000000000001</v>
+      <c r="E16" s="8" t="n">
+        <v>99.7</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>126.8</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="8" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1842,7 +1839,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="16" t="n">
+      <c r="R16" s="15" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1857,7 +1854,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="15" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1927,7 +1924,7 @@
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="16" t="n">
+      <c r="R17" s="15" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1942,7 +1939,7 @@
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="15" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1968,7 +1965,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2229,7 +2226,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2319,8 +2316,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <v>12.4</v>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2398,7 +2395,7 @@
       <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
       <c r="F23" s="8" t="n">
@@ -2437,7 +2434,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="16" t="n">
+      <c r="R23" s="15" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2452,7 +2449,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="16" t="n">
+      <c r="W23" s="15" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2522,7 +2519,7 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="15" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
@@ -2537,7 +2534,7 @@
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="16" t="n">
+      <c r="W24" s="15" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2818,7 +2815,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
+        <v>28.2</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3032,7 +3029,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="16" t="n">
+      <c r="R30" s="15" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3047,7 +3044,7 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="16" t="n">
+      <c r="W30" s="15" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3117,7 +3114,7 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="16" t="n">
+      <c r="R31" s="15" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3132,7 +3129,7 @@
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="15" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3440,13 +3437,13 @@
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>19</v>
+        <v>18.2</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="O35" s="8" t="n">
         <v>100</v>
@@ -3558,16 +3555,16 @@
         <v>21.4</v>
       </c>
       <c r="W36" s="8" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>94.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3609,10 +3606,10 @@
       <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="8" t="n">
+      <c r="L37" s="15" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" s="15" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3627,7 +3624,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="16" t="n">
+      <c r="R37" s="15" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3642,7 +3639,7 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="16" t="n">
+      <c r="W37" s="15" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3692,7 +3689,7 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>20.7</v>
@@ -3712,7 +3709,7 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="16" t="n">
+      <c r="R38" s="15" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3727,7 +3724,7 @@
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="16" t="n">
+      <c r="W38" s="15" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3774,7 +3771,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -4109,7 +4106,7 @@
         <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4176,7 +4173,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
@@ -4215,7 +4212,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
+        <v>145.3</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>152.7</v>
@@ -4238,7 +4235,7 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="16" t="n">
+      <c r="K45" s="15" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
@@ -4259,7 +4256,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="16" t="n">
+      <c r="R45" s="15" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4274,17 +4271,17 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="16" t="n">
+      <c r="W45" s="15" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>138.1</v>
+        <v>13.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>
@@ -4344,7 +4341,7 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
+      <c r="R46" s="15" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
@@ -4359,7 +4356,7 @@
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="15" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -820,7 +820,7 @@
         <v>33</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>23</v>
+        <v>25.6</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>28.1</v>
@@ -835,7 +835,7 @@
         <v>28.6</v>
       </c>
       <c r="W4" s="8" t="n">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
       <c r="X4" s="8" t="n">
         <v>29.1</v>
@@ -893,19 +893,19 @@
         <v>21.4</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>98.8</v>
+        <v>98.3</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>26.2</v>
@@ -923,13 +923,13 @@
         <v>21.1</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>94.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -978,19 +978,19 @@
         <v>21.3</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>22.5</v>
+        <v>24.9</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>27.3</v>
@@ -1005,7 +1005,7 @@
         <v>28.3</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="X6" s="8" t="n">
         <v>29</v>
@@ -1063,19 +1063,19 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>22.9</v>
+        <v>25.3</v>
       </c>
       <c r="S7" s="8" t="n">
         <v>28</v>
@@ -1090,7 +1090,7 @@
         <v>28.7</v>
       </c>
       <c r="W7" s="8" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
         <v>28.8</v>
@@ -1160,7 +1160,7 @@
         <v>33.3</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="S8" s="8" t="n">
         <v>27.9</v>
@@ -1175,7 +1175,7 @@
         <v>28.1</v>
       </c>
       <c r="W8" s="8" t="n">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
       <c r="X8" s="8" t="n">
         <v>28.2</v>
@@ -1244,7 +1244,7 @@
       <c r="Q9" s="8" t="n">
         <v>155.6</v>
       </c>
-      <c r="R9" s="15" t="n">
+      <c r="R9" s="8" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1259,7 +1259,7 @@
       <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="15" t="n">
+      <c r="W9" s="8" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1318,43 +1318,43 @@
         <v>21.6</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="15" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>31.5</v>
+        <v>27.2</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>69.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>13.7</v>
+        <v>18</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>29.8</v>
+        <v>27.7</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>83.2</v>
+        <v>77.2</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>33.2</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>23.2</v>
+        <v>25.8</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>28.5</v>
@@ -1430,7 +1430,7 @@
         <v>29.5</v>
       </c>
       <c r="W11" s="8" t="n">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>29</v>
@@ -1500,7 +1500,7 @@
         <v>32.8</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>28.7</v>
@@ -1515,7 +1515,7 @@
         <v>29.6</v>
       </c>
       <c r="W12" s="8" t="n">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
       <c r="X12" s="8" t="n">
         <v>30.3</v>
@@ -1573,19 +1573,19 @@
         <v>21</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="O13" s="8" t="n">
-        <v>98.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P13" s="8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>22.5</v>
+        <v>24.3</v>
       </c>
       <c r="S13" s="8" t="n">
         <v>27.3</v>
@@ -1600,7 +1600,7 @@
         <v>26.4</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>27.8</v>
@@ -1658,19 +1658,19 @@
         <v>20.9</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P14" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="S14" s="8" t="n">
         <v>28.2</v>
@@ -1685,7 +1685,7 @@
         <v>26</v>
       </c>
       <c r="W14" s="8" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="X14" s="8" t="n">
         <v>28.6</v>
@@ -1755,7 +1755,7 @@
         <v>30</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>30</v>
@@ -1770,7 +1770,7 @@
         <v>25</v>
       </c>
       <c r="W15" s="8" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>24.3</v>
@@ -1839,7 +1839,7 @@
       <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="15" t="n">
+      <c r="R16" s="8" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1854,7 +1854,7 @@
       <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="15" t="n">
+      <c r="W16" s="8" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1913,43 +1913,43 @@
         <v>20.4</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="15" t="n">
+      <c r="R17" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>31.9</v>
+        <v>28.1</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>72.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>11.8</v>
+        <v>15.5</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="15" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>30</v>
+        <v>27.8</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>82.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>32.2</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>22.8</v>
+        <v>25.3</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>27.8</v>
@@ -2025,7 +2025,7 @@
         <v>28.3</v>
       </c>
       <c r="W18" s="8" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
         <v>29.8</v>
@@ -2083,19 +2083,19 @@
         <v>20.7</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P19" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>23.1</v>
+        <v>25.3</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>28.2</v>
@@ -2110,7 +2110,7 @@
         <v>25.7</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>29.2</v>
@@ -2180,7 +2180,7 @@
         <v>27.9</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>26.9</v>
@@ -2195,7 +2195,7 @@
         <v>25</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="X20" s="8" t="n">
         <v>26.3</v>
@@ -2265,7 +2265,7 @@
         <v>30.1</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>22.3</v>
+        <v>24.4</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>26.9</v>
@@ -2280,7 +2280,7 @@
         <v>26.3</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>28.8</v>
@@ -2350,7 +2350,7 @@
         <v>31</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>29.9</v>
@@ -2365,7 +2365,7 @@
         <v>24</v>
       </c>
       <c r="W22" s="8" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="X22" s="8" t="n">
         <v>26.5</v>
@@ -2434,7 +2434,7 @@
       <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="15" t="n">
+      <c r="R23" s="8" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2449,7 +2449,7 @@
       <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="15" t="n">
+      <c r="W23" s="8" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2519,32 +2519,32 @@
       <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="15" t="n">
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>31.5</v>
+        <v>27.6</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>71.7</v>
+        <v>62.7</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>12.5</v>
+        <v>16.4</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="15" t="n">
+      <c r="W24" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>29.5</v>
+        <v>28</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>88.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
       <c r="M25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="N25" s="8" t="n">
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
@@ -2608,13 +2608,13 @@
         <v>22.1</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>95.3</v>
+        <v>93.3</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>21.5</v>
@@ -2623,13 +2623,13 @@
         <v>21</v>
       </c>
       <c r="X25" s="8" t="n">
-        <v>24.9</v>
+        <v>24.5</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>97</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>31.4</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>21.3</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="8" t="n">
         <v>25.3</v>
@@ -2705,7 +2705,7 @@
         <v>27.2</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="X26" s="8" t="n">
         <v>26.8</v>
@@ -2775,7 +2775,7 @@
         <v>32.9</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>22</v>
+        <v>24.9</v>
       </c>
       <c r="S27" s="8" t="n">
         <v>26.4</v>
@@ -2790,7 +2790,7 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="X27" s="8" t="n">
         <v>30.2</v>
@@ -2860,7 +2860,7 @@
         <v>29.7</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
       <c r="S28" s="8" t="n">
         <v>28.9</v>
@@ -2875,7 +2875,7 @@
         <v>24.4</v>
       </c>
       <c r="W28" s="8" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
         <v>26.3</v>
@@ -2945,7 +2945,7 @@
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>28.8</v>
@@ -2960,7 +2960,7 @@
         <v>25</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>25.9</v>
@@ -3029,7 +3029,7 @@
       <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="8" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3044,7 +3044,7 @@
       <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="8" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3114,32 +3114,32 @@
       <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="15" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>30.2</v>
+        <v>26.8</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>74.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>10.1</v>
+        <v>13.5</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="8" t="n">
         <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>25.6</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P32" s="8" t="n">
         <v>0.2</v>
@@ -3200,7 +3200,7 @@
         <v>29</v>
       </c>
       <c r="R32" s="8" t="n">
-        <v>22.9</v>
+        <v>24.5</v>
       </c>
       <c r="S32" s="8" t="n">
         <v>27.9</v>
@@ -3215,7 +3215,7 @@
         <v>27.1</v>
       </c>
       <c r="W32" s="8" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="X32" s="8" t="n">
         <v>29.1</v>
@@ -3273,19 +3273,19 @@
         <v>20.6</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="8" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
       <c r="S33" s="8" t="n">
         <v>25.2</v>
@@ -3303,13 +3303,13 @@
         <v>22</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>94.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>30.1</v>
       </c>
       <c r="R34" s="8" t="n">
-        <v>24</v>
+        <v>25.6</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>29.9</v>
@@ -3385,7 +3385,7 @@
         <v>26.3</v>
       </c>
       <c r="W34" s="8" t="n">
-        <v>18.6</v>
+        <v>21</v>
       </c>
       <c r="X34" s="8" t="n">
         <v>21.4</v>
@@ -3440,7 +3440,7 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>20.9</v>
@@ -3455,7 +3455,7 @@
         <v>28.3</v>
       </c>
       <c r="R35" s="8" t="n">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
       <c r="S35" s="8" t="n">
         <v>29</v>
@@ -3470,7 +3470,7 @@
         <v>26.3</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>29.3</v>
@@ -3528,19 +3528,19 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>98.8</v>
+        <v>98.3</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="R36" s="8" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="S36" s="8" t="n">
         <v>24.3</v>
@@ -3558,13 +3558,13 @@
         <v>20.8</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>96.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       <c r="L37" s="15" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="15" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3624,7 +3624,7 @@
       <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="15" t="n">
+      <c r="R37" s="8" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3639,7 +3639,7 @@
       <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="15" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3709,32 +3709,32 @@
       <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="15" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>29.1</v>
+        <v>27.1</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="V38" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="15" t="n">
+      <c r="W38" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>87.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>19.5</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="8" t="n">
         <v>22.6</v>
@@ -3795,7 +3795,7 @@
         <v>30.7</v>
       </c>
       <c r="R39" s="8" t="n">
-        <v>23.7</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="8" t="n">
         <v>29.3</v>
@@ -3813,13 +3813,13 @@
         <v>23.9</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>79.3</v>
+        <v>72.2</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>7.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>30.7</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>28.8</v>
@@ -3898,13 +3898,13 @@
         <v>24</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>29.8</v>
+        <v>27.1</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>78.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>20.9</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="N41" s="8" t="n">
         <v>23.2</v>
@@ -3963,7 +3963,7 @@
         <v>29.3</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="8" t="n">
         <v>28.7</v>
@@ -3978,7 +3978,7 @@
         <v>27.1</v>
       </c>
       <c r="W41" s="8" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="8" t="n">
         <v>29.1</v>
@@ -4048,7 +4048,7 @@
         <v>30.9</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>22.7</v>
+        <v>24.9</v>
       </c>
       <c r="S42" s="8" t="n">
         <v>27.6</v>
@@ -4063,7 +4063,7 @@
         <v>27.1</v>
       </c>
       <c r="W42" s="8" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="X42" s="8" t="n">
         <v>29.3</v>
@@ -4121,10 +4121,10 @@
         <v>21.1</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="O43" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="P43" s="8" t="n">
         <v>0.2</v>
@@ -4133,7 +4133,7 @@
         <v>24.7</v>
       </c>
       <c r="R43" s="8" t="n">
-        <v>20.4</v>
+        <v>21.7</v>
       </c>
       <c r="S43" s="8" t="n">
         <v>24</v>
@@ -4151,13 +4151,13 @@
         <v>22</v>
       </c>
       <c r="X43" s="8" t="n">
-        <v>26.4</v>
+        <v>25.1</v>
       </c>
       <c r="Y43" s="8" t="n">
-        <v>88.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="Z43" s="8" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4189,12 +4189,12 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="14" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="8" t="inlineStr"/>
-      <c r="W44" s="14" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
       <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="15" t="n">
+      <c r="R45" s="8" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4271,7 +4271,7 @@
       <c r="V45" s="8" t="n">
         <v>134</v>
       </c>
-      <c r="W45" s="15" t="n">
+      <c r="W45" s="8" t="n">
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4341,32 +4341,32 @@
       <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="15" t="n">
+      <c r="R46" s="8" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>30.7</v>
+        <v>27.4</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>75.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="15" t="n">
+      <c r="W46" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>29.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>83.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/203/203_196906_SF.JPG_post_QA_QC.xlsx
@@ -831,7 +831,7 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -916,7 +916,7 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -1001,7 +1001,7 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1086,7 +1086,7 @@
       <c r="J7" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1171,7 +1171,7 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1256,7 +1256,7 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1427,7 +1427,7 @@
       <c r="J11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1512,7 +1512,7 @@
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1597,7 +1597,7 @@
       <c r="J13" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1682,7 +1682,7 @@
       <c r="J14" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1767,7 +1767,7 @@
       <c r="J15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1852,7 +1852,7 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2022,7 +2022,7 @@
       <c r="J18" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2107,7 +2107,7 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -2192,7 +2192,7 @@
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2277,7 +2277,7 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
@@ -2362,7 +2362,7 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2447,7 +2447,7 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -3028,7 +3028,7 @@
       <c r="J30" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="22" t="n">
         <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3617,7 +3617,7 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="22" t="n">
         <v>17.9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4249,7 +4249,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
+      <c r="K45" s="14" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n">
         <v>10.6</v>
